--- a/testcases/terms-conditions/terms-conditions-core.xlsx
+++ b/testcases/terms-conditions/terms-conditions-core.xlsx
@@ -459,7 +459,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M269"/>
+  <dimension ref="A1:M257"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15" outlineLevelRow="0"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -4090,12 +4090,12 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-036</t>
+          <t xml:space="preserve">TC-TNC-CORE-036</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Column resize does not persist (persistence - non-persistent state)</t>
+          <t>Editor state does not leak between cell selections (NM-3162)</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -4127,24 +4127,27 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default).
-"": persistence</t>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). Two rows with different Left Column content exist</t>
         </is>
       </c>
       <c r="K92" t="inlineStr">
         <is>
-          <t>1. Drag a column resize handle to change a column width</t>
+          <t>1. Click the Left Column cell of row A to open the editor</t>
         </is>
       </c>
       <c r="L92" t="inlineStr">
         <is>
-          <t>The column width changes visually</t>
+          <t>The editor shows row A's content</t>
         </is>
       </c>
       <c r="M92" t="inlineStr"/>
@@ -4162,12 +4165,12 @@
       <c r="J93" t="inlineStr"/>
       <c r="K93" t="inlineStr">
         <is>
-          <t>2. Reload the page</t>
+          <t>2. Note the editor content</t>
         </is>
       </c>
       <c r="L93" t="inlineStr">
         <is>
-          <t>The page reloads</t>
+          <t>Content A is recorded</t>
         </is>
       </c>
       <c r="M93" t="inlineStr"/>
@@ -4185,77 +4188,35 @@
       <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr">
         <is>
-          <t>3. Compare the column width to its pre-drag state</t>
+          <t>3. Click the Left Column cell of row B (dismiss any unsaved-changes dialog by clicking Discard if it appears)</t>
         </is>
       </c>
       <c r="L94" t="inlineStr">
         <is>
-          <t>The column has returned to its default width</t>
+          <t>The editor shows row B's content</t>
         </is>
       </c>
       <c r="M94" t="inlineStr"/>
     </row>
     <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-037</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Editor state does not leak between cell selections (NM-3162)</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D95" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J95" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). Two rows with different Left Column content exist</t>
-        </is>
-      </c>
+      <c r="A95" t="inlineStr"/>
+      <c r="B95" t="inlineStr"/>
+      <c r="C95" t="inlineStr"/>
+      <c r="D95" t="inlineStr"/>
+      <c r="E95" t="inlineStr"/>
+      <c r="F95" t="inlineStr"/>
+      <c r="G95" t="inlineStr"/>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
+      <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr">
         <is>
-          <t>1. Click the Left Column cell of row A to open the editor</t>
+          <t>4. Verify the editor content is row B's content, not row A's</t>
         </is>
       </c>
       <c r="L95" t="inlineStr">
         <is>
-          <t>The editor shows row A's content</t>
+          <t>The content matches row B, not row A</t>
         </is>
       </c>
       <c r="M95" t="inlineStr"/>
@@ -4273,12 +4234,12 @@
       <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr">
         <is>
-          <t>2. Note the editor content</t>
+          <t>5. Click back to row A's Left Column cell (dismiss any dialog if it appears)</t>
         </is>
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>Content A is recorded</t>
+          <t>The editor shows row A's original content</t>
         </is>
       </c>
       <c r="M96" t="inlineStr"/>
@@ -4296,35 +4257,77 @@
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr">
         <is>
-          <t>3. Click the Left Column cell of row B (dismiss any unsaved-changes dialog by clicking Discard if it appears)</t>
+          <t>6. Verify row A's content has not been contaminated by row B's content</t>
         </is>
       </c>
       <c r="L97" t="inlineStr">
         <is>
-          <t>The editor shows row B's content</t>
+          <t>Row A's content is unchanged</t>
         </is>
       </c>
       <c r="M97" t="inlineStr"/>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
-      <c r="B98" t="inlineStr"/>
-      <c r="C98" t="inlineStr"/>
-      <c r="D98" t="inlineStr"/>
-      <c r="E98" t="inlineStr"/>
-      <c r="F98" t="inlineStr"/>
-      <c r="G98" t="inlineStr"/>
-      <c r="H98" t="inlineStr"/>
-      <c r="I98" t="inlineStr"/>
-      <c r="J98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-037</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>Typed HTML entities are stored as escaped literals, not rendered as markup (NM-3163)</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>terms-conditions</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). An existing row with a known name is visible. The grid contains no residue rows that can make the bulk save return HTTP 500</t>
+        </is>
+      </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>4. Verify the editor content is row B's content, not row A's</t>
+          <t>1. Click the Left Column cell of a row to open the editor</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>The content matches row B, not row A</t>
+          <t>The editor opens</t>
         </is>
       </c>
       <c r="M98" t="inlineStr"/>
@@ -4342,12 +4345,12 @@
       <c r="J99" t="inlineStr"/>
       <c r="K99" t="inlineStr">
         <is>
-          <t>5. Click back to row A's Left Column cell (dismiss any dialog if it appears)</t>
+          <t>2. Type the following using keyboard input: &amp;nbsp; &amp;amp; &lt; &gt; &lt;b&gt;bold&lt;/b&gt;</t>
         </is>
       </c>
       <c r="L99" t="inlineStr">
         <is>
-          <t>The editor shows row A's original content</t>
+          <t>The text appears in the editor as literal characters — angle brackets visible as text, not rendered as markup</t>
         </is>
       </c>
       <c r="M99" t="inlineStr"/>
@@ -4365,77 +4368,35 @@
       <c r="J100" t="inlineStr"/>
       <c r="K100" t="inlineStr">
         <is>
-          <t>6. Verify row A's content has not been contaminated by row B's content</t>
+          <t>3. Inspect the editor's inner HTML before saving</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>Row A's content is unchanged</t>
+          <t>The HTML contains: `&lt;p&gt;&amp;amp;nbsp; &amp;amp;amp; &amp;lt; &amp;gt; &amp;lt;b&amp;gt;bold&amp;lt;/b&amp;gt; &amp;lt; &amp;amp;&lt;/p&gt;` — all typed characters are HTML-escaped</t>
         </is>
       </c>
       <c r="M100" t="inlineStr"/>
     </row>
     <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-038</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Typed HTML entities are stored as escaped literals, not rendered as markup (NM-3163)</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J101" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). An existing row with a known name is visible. The grid contains no residue rows that can make the bulk save return HTTP 500</t>
-        </is>
-      </c>
+      <c r="A101" t="inlineStr"/>
+      <c r="B101" t="inlineStr"/>
+      <c r="C101" t="inlineStr"/>
+      <c r="D101" t="inlineStr"/>
+      <c r="E101" t="inlineStr"/>
+      <c r="F101" t="inlineStr"/>
+      <c r="G101" t="inlineStr"/>
+      <c r="H101" t="inlineStr"/>
+      <c r="I101" t="inlineStr"/>
+      <c r="J101" t="inlineStr"/>
       <c r="K101" t="inlineStr">
         <is>
-          <t>1. Click the Left Column cell of a row to open the editor</t>
+          <t>4. Click Save</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>The editor opens</t>
+          <t>Save completes</t>
         </is>
       </c>
       <c r="M101" t="inlineStr"/>
@@ -4453,12 +4414,12 @@
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr">
         <is>
-          <t>2. Type the following using keyboard input: &amp;nbsp; &amp;amp; &lt; &gt; &lt;b&gt;bold&lt;/b&gt;</t>
+          <t>5. Reload the page</t>
         </is>
       </c>
       <c r="L102" t="inlineStr">
         <is>
-          <t>The text appears in the editor as literal characters — angle brackets visible as text, not rendered as markup</t>
+          <t>The page reloads</t>
         </is>
       </c>
       <c r="M102" t="inlineStr"/>
@@ -4476,12 +4437,12 @@
       <c r="J103" t="inlineStr"/>
       <c r="K103" t="inlineStr">
         <is>
-          <t>3. Inspect the editor's inner HTML before saving</t>
+          <t>6. Click the same row's Left Column cell</t>
         </is>
       </c>
       <c r="L103" t="inlineStr">
         <is>
-          <t>The HTML contains: `&lt;p&gt;&amp;amp;nbsp; &amp;amp;amp; &amp;lt; &amp;gt; &amp;lt;b&amp;gt;bold&amp;lt;/b&amp;gt; &amp;lt; &amp;amp;&lt;/p&gt;` — all typed characters are HTML-escaped</t>
+          <t>The editor opens</t>
         </is>
       </c>
       <c r="M103" t="inlineStr"/>
@@ -4499,35 +4460,77 @@
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr">
         <is>
-          <t>4. Click Save</t>
+          <t>7. Verify the text displays as literal characters, not as rendered markup or entity sequences</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>Save completes</t>
+          <t>The typed characters are displayed exactly as literal text</t>
         </is>
       </c>
       <c r="M104" t="inlineStr"/>
     </row>
     <row r="105">
-      <c r="A105" t="inlineStr"/>
-      <c r="B105" t="inlineStr"/>
-      <c r="C105" t="inlineStr"/>
-      <c r="D105" t="inlineStr"/>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr"/>
-      <c r="G105" t="inlineStr"/>
-      <c r="H105" t="inlineStr"/>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
+      <c r="A105" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-038</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>Switching cells with unsaved editor content raises a guard dialog (NM-2191)</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>terms-conditions</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
+        </is>
+      </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>5. Reload the page</t>
+          <t>1. Click the Left Column cell of a row to open the editor</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
         <is>
-          <t>The page reloads</t>
+          <t>The editor opens</t>
         </is>
       </c>
       <c r="M105" t="inlineStr"/>
@@ -4545,12 +4548,12 @@
       <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr">
         <is>
-          <t>6. Click the same row's Left Column cell</t>
+          <t>2. Type additional text into the editor</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
         <is>
-          <t>The editor opens</t>
+          <t>The text appears in the editor</t>
         </is>
       </c>
       <c r="M106" t="inlineStr"/>
@@ -4568,100 +4571,100 @@
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr">
         <is>
-          <t>7. Verify the text displays as literal characters, not as rendered markup or entity sequences</t>
+          <t>3. Click the Left Column cell of a different row</t>
         </is>
       </c>
       <c r="L107" t="inlineStr">
         <is>
-          <t>The typed characters are displayed exactly as literal text</t>
+          <t>An "Unsaved changes" dialog appears with Stay and Discard options</t>
         </is>
       </c>
       <c r="M107" t="inlineStr"/>
     </row>
     <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-039</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Switching cells with unsaved editor content raises a guard dialog (NM-2191)</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
+      <c r="A108" t="inlineStr"/>
+      <c r="B108" t="inlineStr"/>
+      <c r="C108" t="inlineStr"/>
+      <c r="D108" t="inlineStr"/>
+      <c r="E108" t="inlineStr"/>
+      <c r="F108" t="inlineStr"/>
+      <c r="G108" t="inlineStr"/>
+      <c r="H108" t="inlineStr"/>
+      <c r="I108" t="inlineStr"/>
+      <c r="J108" t="inlineStr"/>
+      <c r="K108" t="inlineStr">
+        <is>
+          <t>4. Click Stay</t>
+        </is>
+      </c>
+      <c r="L108" t="inlineStr">
+        <is>
+          <t>The dialog closes; the editor remains on the original row with the typed text intact</t>
+        </is>
+      </c>
+      <c r="M108" t="inlineStr"/>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-039</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>Discarding unsaved editor content on cell switch clears the edit</t>
+        </is>
+      </c>
+      <c r="C109" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D108" t="inlineStr">
+      <c r="D109" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E108" t="inlineStr">
+      <c r="E109" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F108" t="inlineStr">
+      <c r="F109" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="G109" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H108" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr">
+      <c r="I109" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J108" t="inlineStr">
+      <c r="J109" t="inlineStr">
         <is>
           <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
         </is>
       </c>
-      <c r="K108" t="inlineStr">
+      <c r="K109" t="inlineStr">
         <is>
           <t>1. Click the Left Column cell of a row to open the editor</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
+      <c r="L109" t="inlineStr">
         <is>
           <t>The editor opens</t>
-        </is>
-      </c>
-      <c r="M108" t="inlineStr"/>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr"/>
-      <c r="B109" t="inlineStr"/>
-      <c r="C109" t="inlineStr"/>
-      <c r="D109" t="inlineStr"/>
-      <c r="E109" t="inlineStr"/>
-      <c r="F109" t="inlineStr"/>
-      <c r="G109" t="inlineStr"/>
-      <c r="H109" t="inlineStr"/>
-      <c r="I109" t="inlineStr"/>
-      <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>2. Type additional text into the editor</t>
-        </is>
-      </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>The text appears in the editor</t>
         </is>
       </c>
       <c r="M109" t="inlineStr"/>
@@ -4679,12 +4682,12 @@
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr">
         <is>
-          <t>3. Click the Left Column cell of a different row</t>
+          <t>2. Type additional text into the editor</t>
         </is>
       </c>
       <c r="L110" t="inlineStr">
         <is>
-          <t>An "Unsaved changes" dialog appears with Stay and Discard options</t>
+          <t>The text appears</t>
         </is>
       </c>
       <c r="M110" t="inlineStr"/>
@@ -4702,77 +4705,35 @@
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr">
         <is>
-          <t>4. Click Stay</t>
+          <t>3. Click the Left Column cell of a different row</t>
         </is>
       </c>
       <c r="L111" t="inlineStr">
         <is>
-          <t>The dialog closes; the editor remains on the original row with the typed text intact</t>
+          <t>The "Unsaved changes" dialog appears</t>
         </is>
       </c>
       <c r="M111" t="inlineStr"/>
     </row>
     <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-040</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Discarding unsaved editor content on cell switch clears the edit</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J112" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
-        </is>
-      </c>
+      <c r="A112" t="inlineStr"/>
+      <c r="B112" t="inlineStr"/>
+      <c r="C112" t="inlineStr"/>
+      <c r="D112" t="inlineStr"/>
+      <c r="E112" t="inlineStr"/>
+      <c r="F112" t="inlineStr"/>
+      <c r="G112" t="inlineStr"/>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
+      <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr">
         <is>
-          <t>1. Click the Left Column cell of a row to open the editor</t>
+          <t>4. Click Discard</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>The editor opens</t>
+          <t>The dialog closes; the editor switches to the new row; the typed text from step 2 is discarded</t>
         </is>
       </c>
       <c r="M112" t="inlineStr"/>
@@ -4790,35 +4751,77 @@
       <c r="J113" t="inlineStr"/>
       <c r="K113" t="inlineStr">
         <is>
-          <t>2. Type additional text into the editor</t>
+          <t>5. Click back to the original row's Left Column cell</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>The text appears</t>
+          <t>The editor shows the original row's content WITHOUT the text typed in step 2</t>
         </is>
       </c>
       <c r="M113" t="inlineStr"/>
     </row>
     <row r="114">
-      <c r="A114" t="inlineStr"/>
-      <c r="B114" t="inlineStr"/>
-      <c r="C114" t="inlineStr"/>
-      <c r="D114" t="inlineStr"/>
-      <c r="E114" t="inlineStr"/>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr"/>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
+      <c r="A114" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-040</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Changing the language filter with unsaved edits raises a guard dialog (NM-2191)</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>terms-conditions</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
+        </is>
+      </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>3. Click the Left Column cell of a different row</t>
+          <t>1. Change an existing row's Name to a different unique value</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
         <is>
-          <t>The "Unsaved changes" dialog appears</t>
+          <t>Save becomes enabled</t>
         </is>
       </c>
       <c r="M114" t="inlineStr"/>
@@ -4836,12 +4839,12 @@
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr">
         <is>
-          <t>4. Click Discard</t>
+          <t>2. Select a different language in the page-level filter</t>
         </is>
       </c>
       <c r="L115" t="inlineStr">
         <is>
-          <t>The dialog closes; the editor switches to the new row; the typed text from step 2 is discarded</t>
+          <t>A warning dialog appears with title "Unsaved changes", body "Are you sure you want to leave this view? Any unsaved changes will be lost.", and buttons Stay / Discard</t>
         </is>
       </c>
       <c r="M115" t="inlineStr"/>
@@ -4859,100 +4862,100 @@
       <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr">
         <is>
-          <t>5. Click back to the original row's Left Column cell</t>
+          <t>3. Click Stay</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>The editor shows the original row's content WITHOUT the text typed in step 2</t>
+          <t>The dialog closes; the filter has not changed; the edited value is still present; Save is still enabled</t>
         </is>
       </c>
       <c r="M116" t="inlineStr"/>
     </row>
     <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-041</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Changing the language filter with unsaved edits raises a guard dialog (NM-2191)</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
+      <c r="A117" t="inlineStr"/>
+      <c r="B117" t="inlineStr"/>
+      <c r="C117" t="inlineStr"/>
+      <c r="D117" t="inlineStr"/>
+      <c r="E117" t="inlineStr"/>
+      <c r="F117" t="inlineStr"/>
+      <c r="G117" t="inlineStr"/>
+      <c r="H117" t="inlineStr"/>
+      <c r="I117" t="inlineStr"/>
+      <c r="J117" t="inlineStr"/>
+      <c r="K117" t="inlineStr">
+        <is>
+          <t>4. Restore the original name</t>
+        </is>
+      </c>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>Save returns to disabled</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-041</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Editor content across columns uses the same shared panel</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr">
+      <c r="D118" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E117" t="inlineStr">
+      <c r="E118" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F117" t="inlineStr">
+      <c r="F118" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="G118" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H117" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I117" t="inlineStr">
+      <c r="I118" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J117" t="inlineStr">
+      <c r="J118" t="inlineStr">
         <is>
           <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
         </is>
       </c>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>1. Change an existing row's Name to a different unique value</t>
-        </is>
-      </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>Save becomes enabled</t>
-        </is>
-      </c>
-      <c r="M117" t="inlineStr"/>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr"/>
-      <c r="B118" t="inlineStr"/>
-      <c r="C118" t="inlineStr"/>
-      <c r="D118" t="inlineStr"/>
-      <c r="E118" t="inlineStr"/>
-      <c r="F118" t="inlineStr"/>
-      <c r="G118" t="inlineStr"/>
-      <c r="H118" t="inlineStr"/>
-      <c r="I118" t="inlineStr"/>
-      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr">
         <is>
-          <t>2. Select a different language in the page-level filter</t>
+          <t>1. Click the Left Column cell of a row</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
         <is>
-          <t>A warning dialog appears with title "Unsaved changes", body "Are you sure you want to leave this view? Any unsaved changes will be lost.", and buttons Stay / Discard</t>
+          <t>The editor opens showing the Left Column content</t>
         </is>
       </c>
       <c r="M118" t="inlineStr"/>
@@ -4970,12 +4973,12 @@
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr">
         <is>
-          <t>3. Click Stay</t>
+          <t>2. Click the Right Column cell of the same row (dismiss any unsaved-changes dialog if it appears)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
         <is>
-          <t>The dialog closes; the filter has not changed; the edited value is still present; Save is still enabled</t>
+          <t>The editor switches to show the Right Column content</t>
         </is>
       </c>
       <c r="M119" t="inlineStr"/>
@@ -4993,12 +4996,12 @@
       <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr">
         <is>
-          <t>4. Restore the original name</t>
+          <t>3. Click the Bottom Column cell of the same row (dismiss any dialog if it appears)</t>
         </is>
       </c>
       <c r="L120" t="inlineStr">
         <is>
-          <t>Save returns to disabled</t>
+          <t>The editor switches to show the Bottom Column content</t>
         </is>
       </c>
       <c r="M120" t="inlineStr"/>
@@ -5006,12 +5009,12 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-042</t>
+          <t xml:space="preserve">TC-TNC-CORE-042</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Editor content across columns uses the same shared panel</t>
+          <t>No guard dialog when editing a different row while one row is name-dirty</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
@@ -5053,17 +5056,17 @@
       </c>
       <c r="J121" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). At least two rows are visible</t>
         </is>
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>1. Click the Left Column cell of a row</t>
+          <t>1. Change row A's Name to a different unique value</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
         <is>
-          <t>The editor opens showing the Left Column content</t>
+          <t>Save becomes enabled</t>
         </is>
       </c>
       <c r="M121" t="inlineStr"/>
@@ -5081,12 +5084,12 @@
       <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr">
         <is>
-          <t>2. Click the Right Column cell of the same row (dismiss any unsaved-changes dialog if it appears)</t>
+          <t>2. Click row B's Name input</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>The editor switches to show the Right Column content</t>
+          <t>Focus moves to row B; NO guard dialog appears; row A's edit remains</t>
         </is>
       </c>
       <c r="M122" t="inlineStr"/>
@@ -5104,12 +5107,12 @@
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr">
         <is>
-          <t>3. Click the Bottom Column cell of the same row (dismiss any dialog if it appears)</t>
+          <t>3. Type a value into row B's Name</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
         <is>
-          <t>The editor switches to show the Bottom Column content</t>
+          <t>Both rows are now edited simultaneously; no warning was shown</t>
         </is>
       </c>
       <c r="M123" t="inlineStr"/>
@@ -5117,12 +5120,12 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-043</t>
+          <t xml:space="preserve">TC-TNC-CORE-043</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>No guard dialog when editing a different row while one row is name-dirty</t>
+          <t>Valid save should succeed even when residue rows are present</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
@@ -5159,17 +5162,17 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). At least two rows are visible</t>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). The grid contains at least one residue row with extreme content (e.g. 260-char name, special-character name, or RTE probe sentinels from prior test runs)</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>1. Change row A's Name to a different unique value</t>
+          <t>1. Change a clean row's language to a different value</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
@@ -5192,12 +5195,12 @@
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr">
         <is>
-          <t>2. Click row B's Name input</t>
+          <t>2. Click Save and observe the network response</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
         <is>
-          <t>Focus moves to row B; NO guard dialog appears; row A's edit remains</t>
+          <t>The server returns HTTP 500 with body `{"success":false,"message":"Something unexpected has happened...","statusCode":"Internal Server Error!"}`</t>
         </is>
       </c>
       <c r="M125" t="inlineStr"/>
@@ -5215,12 +5218,12 @@
       <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr">
         <is>
-          <t>3. Type a value into row B's Name</t>
+          <t>3. Reload the page and verify the language change</t>
         </is>
       </c>
       <c r="L126" t="inlineStr">
         <is>
-          <t>Both rows are now edited simultaneously; no warning was shown</t>
+          <t>The language change is NOT persisted — the entire batch was discarded</t>
         </is>
       </c>
       <c r="M126" t="inlineStr"/>
@@ -5228,12 +5231,12 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-044</t>
+          <t xml:space="preserve">TC-TNC-CORE-044</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Valid save should succeed even when residue rows are present</t>
+          <t>UI shows success when save returns HTTP 500 — silent data loss</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
@@ -5270,22 +5273,22 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Skipped</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). The grid contains at least one residue row with extreme content (e.g. 260-char name, special-character name, or RTE probe sentinels from prior test runs)</t>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A save has just returned a non-2xx response (trigger: grid containing residue rows that can make bulk saves return HTTP 500, or any server-side failure)</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>1. Change a clean row's language to a different value</t>
+          <t>1. Observe the UI immediately after the failed save</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
         <is>
-          <t>Save becomes enabled</t>
+          <t>The Save button transitions from enabled to disabled — identical to a successful save</t>
         </is>
       </c>
       <c r="M127" t="inlineStr"/>
@@ -5303,12 +5306,12 @@
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr">
         <is>
-          <t>2. Click Save and observe the network response</t>
+          <t>2. Look for any error toast, banner, inline message, or console error</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>The server returns HTTP 500 with body `{"success":false,"message":"Something unexpected has happened...","statusCode":"Internal Server Error!"}`</t>
+          <t>None is present — no user-facing error signal of any kind</t>
         </is>
       </c>
       <c r="M128" t="inlineStr"/>
@@ -5326,12 +5329,12 @@
       <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr">
         <is>
-          <t>3. Reload the page and verify the language change</t>
+          <t>3. Reload the page and verify the edit</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>The language change is NOT persisted — the entire batch was discarded</t>
+          <t>The edit is NOT persisted — data was silently lost</t>
         </is>
       </c>
       <c r="M129" t="inlineStr"/>
@@ -5339,12 +5342,12 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-045</t>
+          <t xml:space="preserve">TC-TNC-CORE-045</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>UI shows success when save returns HTTP 500 — silent data loss</t>
+          <t>Bold formatting round-trip — &lt;strong&gt; persists through save and reload</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
@@ -5381,22 +5384,22 @@
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A save has just returned a non-2xx response (trigger: grid containing residue rows that can make bulk saves return HTTP 500, or any server-side failure)</t>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>1. Observe the UI immediately after the failed save</t>
+          <t>1. Click the Left Column cell of a row to open the editor</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
         <is>
-          <t>The Save button transitions from enabled to disabled — identical to a successful save</t>
+          <t>The editor opens</t>
         </is>
       </c>
       <c r="M130" t="inlineStr"/>
@@ -5414,12 +5417,12 @@
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr">
         <is>
-          <t>2. Look for any error toast, banner, inline message, or console error</t>
+          <t>2. Select text and apply Bold via the toolbar</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
         <is>
-          <t>None is present — no user-facing error signal of any kind</t>
+          <t>The editor shows `&lt;strong&gt;` markup around the selection</t>
         </is>
       </c>
       <c r="M131" t="inlineStr"/>
@@ -5437,72 +5440,30 @@
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr">
         <is>
-          <t>3. Reload the page and verify the edit</t>
+          <t>3. Click Save</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>The edit is NOT persisted — data was silently lost</t>
+          <t>Save completes</t>
         </is>
       </c>
       <c r="M132" t="inlineStr"/>
     </row>
     <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-046</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>Bold formatting round-trip — &lt;strong&gt; persists through save and reload</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H133" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="J133" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
-        </is>
-      </c>
+      <c r="A133" t="inlineStr"/>
+      <c r="B133" t="inlineStr"/>
+      <c r="C133" t="inlineStr"/>
+      <c r="D133" t="inlineStr"/>
+      <c r="E133" t="inlineStr"/>
+      <c r="F133" t="inlineStr"/>
+      <c r="G133" t="inlineStr"/>
+      <c r="H133" t="inlineStr"/>
+      <c r="I133" t="inlineStr"/>
+      <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr">
         <is>
-          <t>1. Click the Left Column cell of a row to open the editor</t>
+          <t>4. Reload the page and reopen the same cell</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -5525,35 +5486,78 @@
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr">
         <is>
-          <t>2. Select text and apply Bold via the toolbar</t>
+          <t>5. Verify the Bold formatting is still applied</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
         <is>
-          <t>The editor shows `&lt;strong&gt;` markup around the selection</t>
+          <t>NOT YET CONFIRMED — whether `&lt;strong&gt;` tags survive save + reload has not been cleanly measured</t>
         </is>
       </c>
       <c r="M134" t="inlineStr"/>
     </row>
     <row r="135">
-      <c r="A135" t="inlineStr"/>
-      <c r="B135" t="inlineStr"/>
-      <c r="C135" t="inlineStr"/>
-      <c r="D135" t="inlineStr"/>
-      <c r="E135" t="inlineStr"/>
-      <c r="F135" t="inlineStr"/>
-      <c r="G135" t="inlineStr"/>
-      <c r="H135" t="inlineStr"/>
-      <c r="I135" t="inlineStr"/>
-      <c r="J135" t="inlineStr"/>
+      <c r="A135" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-046</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>RTE entity encoding — ampersand typed persists as double-escaped entity</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>terms-conditions</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G135" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H135" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="J135" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row with a known unique name exists.
+"": persistence</t>
+        </is>
+      </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>3. Click Save</t>
+          <t>1. Click the Left Column cell of the target row</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
         <is>
-          <t>Save completes</t>
+          <t>The editor opens showing existing content</t>
         </is>
       </c>
       <c r="M135" t="inlineStr"/>
@@ -5571,12 +5575,12 @@
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>4. Reload the page and reopen the same cell</t>
+          <t>2. Clear existing content and type &amp; using keyboard</t>
         </is>
       </c>
       <c r="L136" t="inlineStr">
         <is>
-          <t>The editor opens</t>
+          <t>The editor shows `&amp;` visually</t>
         </is>
       </c>
       <c r="M136" t="inlineStr"/>
@@ -5594,101 +5598,101 @@
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr">
         <is>
-          <t>5. Verify the Bold formatting is still applied</t>
+          <t>3. Click Save</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>NOT YET CONFIRMED — whether `&lt;strong&gt;` tags survive save + reload has not been cleanly measured</t>
+          <t>Save completes (HTTP 2xx)</t>
         </is>
       </c>
       <c r="M137" t="inlineStr"/>
     </row>
     <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-047</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>RTE entity encoding — ampersand typed persists as double-escaped entity</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
+      <c r="A138" t="inlineStr"/>
+      <c r="B138" t="inlineStr"/>
+      <c r="C138" t="inlineStr"/>
+      <c r="D138" t="inlineStr"/>
+      <c r="E138" t="inlineStr"/>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>4. Reload the page and click the same Left Column cell</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr">
+        <is>
+          <t>The editor shows `&amp;` — stored as `&amp;amp;` in HTML, rendered as literal ampersand</t>
+        </is>
+      </c>
+      <c r="M138" t="inlineStr"/>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-047</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>RTE entity encoding — HTML entity reference typed persists as double-escaped</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr">
+      <c r="D139" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E138" t="inlineStr">
+      <c r="E139" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F138" t="inlineStr">
+      <c r="F139" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="G139" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H138" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J139" t="inlineStr">
         <is>
           <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row with a known unique name exists.
 "": persistence</t>
         </is>
       </c>
-      <c r="K138" t="inlineStr">
+      <c r="K139" t="inlineStr">
         <is>
           <t>1. Click the Left Column cell of the target row</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>The editor opens showing existing content</t>
-        </is>
-      </c>
-      <c r="M138" t="inlineStr"/>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr"/>
-      <c r="B139" t="inlineStr"/>
-      <c r="C139" t="inlineStr"/>
-      <c r="D139" t="inlineStr"/>
-      <c r="E139" t="inlineStr"/>
-      <c r="F139" t="inlineStr"/>
-      <c r="G139" t="inlineStr"/>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
-      <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>2. Clear existing content and type &amp; using keyboard</t>
-        </is>
-      </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>The editor shows `&amp;` visually</t>
+          <t>The editor opens</t>
         </is>
       </c>
       <c r="M139" t="inlineStr"/>
@@ -5706,12 +5710,12 @@
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr">
         <is>
-          <t>3. Click Save</t>
+          <t>2. Clear existing content and type the literal characters &amp;nbsp</t>
         </is>
       </c>
       <c r="L140" t="inlineStr">
         <is>
-          <t>Save completes (HTTP 2xx)</t>
+          <t>The editor shows `&amp;nbsp;` as visible text (not a space)</t>
         </is>
       </c>
       <c r="M140" t="inlineStr"/>
@@ -5729,78 +5733,35 @@
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr">
         <is>
-          <t>4. Reload the page and click the same Left Column cell</t>
+          <t>3. using keyboard</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>The editor shows `&amp;` — stored as `&amp;amp;` in HTML, rendered as literal ampersand</t>
+          <t>Save completes</t>
         </is>
       </c>
       <c r="M141" t="inlineStr"/>
     </row>
     <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-048</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>RTE entity encoding — HTML entity reference typed persists as double-escaped</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D142" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H142" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I142" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J142" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row with a known unique name exists.
-"": persistence</t>
-        </is>
-      </c>
+      <c r="A142" t="inlineStr"/>
+      <c r="B142" t="inlineStr"/>
+      <c r="C142" t="inlineStr"/>
+      <c r="D142" t="inlineStr"/>
+      <c r="E142" t="inlineStr"/>
+      <c r="F142" t="inlineStr"/>
+      <c r="G142" t="inlineStr"/>
+      <c r="H142" t="inlineStr"/>
+      <c r="I142" t="inlineStr"/>
+      <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr">
         <is>
-          <t>1. Click the Left Column cell of the target row</t>
+          <t>4. Click Save</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
         <is>
-          <t>The editor opens</t>
+          <t>The editor shows `&amp;nbsp;` as visible text — stored as `&amp;amp;nbsp;`</t>
         </is>
       </c>
       <c r="M142" t="inlineStr"/>
@@ -5818,35 +5779,74 @@
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr">
         <is>
-          <t>2. Clear existing content and type the literal characters &amp;nbsp</t>
-        </is>
-      </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>The editor shows `&amp;nbsp;` as visible text (not a space)</t>
-        </is>
-      </c>
+          <t>5. Reload the page and click the same Left Column cell</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr"/>
       <c r="M143" t="inlineStr"/>
     </row>
     <row r="144">
-      <c r="A144" t="inlineStr"/>
-      <c r="B144" t="inlineStr"/>
-      <c r="C144" t="inlineStr"/>
-      <c r="D144" t="inlineStr"/>
-      <c r="E144" t="inlineStr"/>
-      <c r="F144" t="inlineStr"/>
-      <c r="G144" t="inlineStr"/>
-      <c r="H144" t="inlineStr"/>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
+      <c r="A144" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-048</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>RTE entity encoding — angle brackets typed persist as escaped entities</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>terms-conditions</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row with a known unique name exists.
+"": persistence</t>
+        </is>
+      </c>
       <c r="K144" t="inlineStr">
         <is>
-          <t>3. using keyboard</t>
+          <t>1. Click the Right Column cell of the target row</t>
         </is>
       </c>
       <c r="L144" t="inlineStr">
         <is>
-          <t>Save completes</t>
+          <t>The editor opens</t>
         </is>
       </c>
       <c r="M144" t="inlineStr"/>
@@ -5864,12 +5864,12 @@
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr">
         <is>
-          <t>4. Click Save</t>
+          <t>2. Clear existing content and type &lt;b&gt;bold&lt;/b&gt; using keyboard</t>
         </is>
       </c>
       <c r="L145" t="inlineStr">
         <is>
-          <t>The editor shows `&amp;nbsp;` as visible text — stored as `&amp;amp;nbsp;`</t>
+          <t>The editor shows `&lt;b&gt;bold&lt;/b&gt;` as visible text (no bold rendering)</t>
         </is>
       </c>
       <c r="M145" t="inlineStr"/>
@@ -5887,97 +5887,102 @@
       <c r="J146" t="inlineStr"/>
       <c r="K146" t="inlineStr">
         <is>
-          <t>5. Reload the page and click the same Left Column cell</t>
-        </is>
-      </c>
-      <c r="L146" t="inlineStr"/>
+          <t>3. Click Save</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>Save completes</t>
+        </is>
+      </c>
       <c r="M146" t="inlineStr"/>
     </row>
     <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-049</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>RTE entity encoding — angle brackets typed persist as escaped entities</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
+      <c r="A147" t="inlineStr"/>
+      <c r="B147" t="inlineStr"/>
+      <c r="C147" t="inlineStr"/>
+      <c r="D147" t="inlineStr"/>
+      <c r="E147" t="inlineStr"/>
+      <c r="F147" t="inlineStr"/>
+      <c r="G147" t="inlineStr"/>
+      <c r="H147" t="inlineStr"/>
+      <c r="I147" t="inlineStr"/>
+      <c r="J147" t="inlineStr"/>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>4. Reload the page and click the same Right Column cell</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>The editor shows `&lt;b&gt;bold&lt;/b&gt;` as visible text — stored as `&amp;lt;b&amp;gt;bold&amp;lt;/b&amp;gt;`</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr"/>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-049</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>RTE entity encoding — nested markup with entities persists byte-exact</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D147" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E147" t="inlineStr">
+      <c r="E148" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
+Application: Navigator
+Sample input 1: "x"</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H147" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I147" t="inlineStr">
+      <c r="I148" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J147" t="inlineStr">
+      <c r="J148" t="inlineStr">
         <is>
           <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row with a known unique name exists.
 "": persistence</t>
         </is>
       </c>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>1. Click the Right Column cell of the target row</t>
-        </is>
-      </c>
-      <c r="L147" t="inlineStr">
+      <c r="K148" t="inlineStr">
+        <is>
+          <t>1. Click the Bottom Column cell of the target row</t>
+        </is>
+      </c>
+      <c r="L148" t="inlineStr">
         <is>
           <t>The editor opens</t>
-        </is>
-      </c>
-      <c r="M147" t="inlineStr"/>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr"/>
-      <c r="B148" t="inlineStr"/>
-      <c r="C148" t="inlineStr"/>
-      <c r="D148" t="inlineStr"/>
-      <c r="E148" t="inlineStr"/>
-      <c r="F148" t="inlineStr"/>
-      <c r="G148" t="inlineStr"/>
-      <c r="H148" t="inlineStr"/>
-      <c r="I148" t="inlineStr"/>
-      <c r="J148" t="inlineStr"/>
-      <c r="K148" t="inlineStr">
-        <is>
-          <t>2. Clear existing content and type &lt;b&gt;bold&lt;/b&gt; using keyboard</t>
-        </is>
-      </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>The editor shows `&lt;b&gt;bold&lt;/b&gt;` as visible text (no bold rendering)</t>
         </is>
       </c>
       <c r="M148" t="inlineStr"/>
@@ -5995,12 +6000,12 @@
       <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr">
         <is>
-          <t>3. Click Save</t>
+          <t>2. Clear existing content and type &lt;div class="x"&gt;&amp;amp; &amp;lt;span&amp;gt;&lt;/div&gt; using keyboard</t>
         </is>
       </c>
       <c r="L149" t="inlineStr">
         <is>
-          <t>Save completes</t>
+          <t>The editor shows the typed string as visible text</t>
         </is>
       </c>
       <c r="M149" t="inlineStr"/>
@@ -6018,102 +6023,101 @@
       <c r="J150" t="inlineStr"/>
       <c r="K150" t="inlineStr">
         <is>
-          <t>4. Reload the page and click the same Right Column cell</t>
+          <t>3. Click Save</t>
         </is>
       </c>
       <c r="L150" t="inlineStr">
         <is>
-          <t>The editor shows `&lt;b&gt;bold&lt;/b&gt;` as visible text — stored as `&amp;lt;b&amp;gt;bold&amp;lt;/b&amp;gt;`</t>
+          <t>Save completes</t>
         </is>
       </c>
       <c r="M150" t="inlineStr"/>
     </row>
     <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-050</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>RTE entity encoding — nested markup with entities persists byte-exact</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
+      <c r="A151" t="inlineStr"/>
+      <c r="B151" t="inlineStr"/>
+      <c r="C151" t="inlineStr"/>
+      <c r="D151" t="inlineStr"/>
+      <c r="E151" t="inlineStr"/>
+      <c r="F151" t="inlineStr"/>
+      <c r="G151" t="inlineStr"/>
+      <c r="H151" t="inlineStr"/>
+      <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
+      <c r="K151" t="inlineStr">
+        <is>
+          <t>4. Reload the page and click the same Bottom Column cell</t>
+        </is>
+      </c>
+      <c r="L151" t="inlineStr">
+        <is>
+          <t>The editor shows the exact typed string — all characters preserved through double-escaping</t>
+        </is>
+      </c>
+      <c r="M151" t="inlineStr"/>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-050</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>RTE empty content — clearing a cell and saving persists empty state</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D151" t="inlineStr">
+      <c r="D152" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E151" t="inlineStr">
+      <c r="E152" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator
-Sample input 1: "x"</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="G152" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H151" t="inlineStr">
+      <c r="H152" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I151" t="inlineStr">
+      <c r="I152" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J151" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row with a known unique name exists.
+      <c r="J152" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row with existing content in Left Column.
 "": persistence</t>
         </is>
       </c>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>1. Click the Bottom Column cell of the target row</t>
-        </is>
-      </c>
-      <c r="L151" t="inlineStr">
-        <is>
-          <t>The editor opens</t>
-        </is>
-      </c>
-      <c r="M151" t="inlineStr"/>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr"/>
-      <c r="B152" t="inlineStr"/>
-      <c r="C152" t="inlineStr"/>
-      <c r="D152" t="inlineStr"/>
-      <c r="E152" t="inlineStr"/>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr"/>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
       <c r="K152" t="inlineStr">
         <is>
-          <t>2. Clear existing content and type &lt;div class="x"&gt;&amp;amp; &amp;lt;span&amp;gt;&lt;/div&gt; using keyboard</t>
+          <t>1. Click the Left Column cell</t>
         </is>
       </c>
       <c r="L152" t="inlineStr">
         <is>
-          <t>The editor shows the typed string as visible text</t>
+          <t>The editor opens with existing content</t>
         </is>
       </c>
       <c r="M152" t="inlineStr"/>
@@ -6131,12 +6135,12 @@
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr">
         <is>
-          <t>3. Click Save</t>
+          <t>2. Select all content and delete it</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
         <is>
-          <t>Save completes</t>
+          <t>The editor is empty</t>
         </is>
       </c>
       <c r="M153" t="inlineStr"/>
@@ -6154,101 +6158,101 @@
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr">
         <is>
-          <t>4. Reload the page and click the same Bottom Column cell</t>
+          <t>3. Click Save</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
         <is>
-          <t>The editor shows the exact typed string — all characters preserved through double-escaping</t>
+          <t>Save completes</t>
         </is>
       </c>
       <c r="M154" t="inlineStr"/>
     </row>
     <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-051</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>RTE empty content — clearing a cell and saving persists empty state</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
+      <c r="A155" t="inlineStr"/>
+      <c r="B155" t="inlineStr"/>
+      <c r="C155" t="inlineStr"/>
+      <c r="D155" t="inlineStr"/>
+      <c r="E155" t="inlineStr"/>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr"/>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>4. Reload the page and click the same Left Column cell</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>The editor opens empty — the cleared state persisted</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr"/>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-051</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>RTE whitespace-only content persists through save and reload</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D156" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E155" t="inlineStr">
+      <c r="E156" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F155" t="inlineStr">
+      <c r="F156" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="G156" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="H156" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J155" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row with existing content in Left Column.
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row with a known unique name exists.
 "": persistence</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
-        <is>
-          <t>1. Click the Left Column cell</t>
-        </is>
-      </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>The editor opens with existing content</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr"/>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr"/>
-      <c r="B156" t="inlineStr"/>
-      <c r="C156" t="inlineStr"/>
-      <c r="D156" t="inlineStr"/>
-      <c r="E156" t="inlineStr"/>
-      <c r="F156" t="inlineStr"/>
-      <c r="G156" t="inlineStr"/>
-      <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr">
         <is>
-          <t>2. Select all content and delete it</t>
+          <t>1. Click the Right Column cell of the target row</t>
         </is>
       </c>
       <c r="L156" t="inlineStr">
         <is>
-          <t>The editor is empty</t>
+          <t>The editor opens</t>
         </is>
       </c>
       <c r="M156" t="inlineStr"/>
@@ -6266,12 +6270,12 @@
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr">
         <is>
-          <t>3. Click Save</t>
+          <t>2. Clear existing content and type three space characters</t>
         </is>
       </c>
       <c r="L157" t="inlineStr">
         <is>
-          <t>Save completes</t>
+          <t>The editor shows whitespace</t>
         </is>
       </c>
       <c r="M157" t="inlineStr"/>
@@ -6289,101 +6293,101 @@
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr">
         <is>
-          <t>4. Reload the page and click the same Left Column cell</t>
+          <t>3. Click Save</t>
         </is>
       </c>
       <c r="L158" t="inlineStr">
         <is>
-          <t>The editor opens empty — the cleared state persisted</t>
+          <t>Save completes</t>
         </is>
       </c>
       <c r="M158" t="inlineStr"/>
     </row>
     <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-052</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>RTE whitespace-only content persists through save and reload</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
+      <c r="A159" t="inlineStr"/>
+      <c r="B159" t="inlineStr"/>
+      <c r="C159" t="inlineStr"/>
+      <c r="D159" t="inlineStr"/>
+      <c r="E159" t="inlineStr"/>
+      <c r="F159" t="inlineStr"/>
+      <c r="G159" t="inlineStr"/>
+      <c r="H159" t="inlineStr"/>
+      <c r="I159" t="inlineStr"/>
+      <c r="J159" t="inlineStr"/>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>4. Reload the page and click the same Right Column cell</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>The editor shows whitespace content — spaces persisted</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr"/>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-052</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>RTE long content (300 characters) persists byte-exact through save and reload</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D159" t="inlineStr">
+      <c r="D160" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E159" t="inlineStr">
+      <c r="E160" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F159" t="inlineStr">
+      <c r="F160" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="G160" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H159" t="inlineStr">
+      <c r="H160" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr">
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
         <is>
           <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row with a known unique name exists.
 "": persistence</t>
         </is>
       </c>
-      <c r="K159" t="inlineStr">
-        <is>
-          <t>1. Click the Right Column cell of the target row</t>
-        </is>
-      </c>
-      <c r="L159" t="inlineStr">
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>1. Click the Left Column cell of the target row</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
         <is>
           <t>The editor opens</t>
-        </is>
-      </c>
-      <c r="M159" t="inlineStr"/>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr"/>
-      <c r="B160" t="inlineStr"/>
-      <c r="C160" t="inlineStr"/>
-      <c r="D160" t="inlineStr"/>
-      <c r="E160" t="inlineStr"/>
-      <c r="F160" t="inlineStr"/>
-      <c r="G160" t="inlineStr"/>
-      <c r="H160" t="inlineStr"/>
-      <c r="I160" t="inlineStr"/>
-      <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>2. Clear existing content and type three space characters</t>
-        </is>
-      </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>The editor shows whitespace</t>
         </is>
       </c>
       <c r="M160" t="inlineStr"/>
@@ -6401,12 +6405,12 @@
       <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr">
         <is>
-          <t>3. Click Save</t>
+          <t>2. Clear existing content and type a 300-character string using keyboard</t>
         </is>
       </c>
       <c r="L161" t="inlineStr">
         <is>
-          <t>Save completes</t>
+          <t>The editor shows all 300 characters</t>
         </is>
       </c>
       <c r="M161" t="inlineStr"/>
@@ -6424,101 +6428,101 @@
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr">
         <is>
-          <t>4. Reload the page and click the same Right Column cell</t>
+          <t>3. Click Save</t>
         </is>
       </c>
       <c r="L162" t="inlineStr">
         <is>
-          <t>The editor shows whitespace content — spaces persisted</t>
+          <t>Save completes</t>
         </is>
       </c>
       <c r="M162" t="inlineStr"/>
     </row>
     <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-053</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>RTE long content (300 characters) persists byte-exact through save and reload</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
+      <c r="A163" t="inlineStr"/>
+      <c r="B163" t="inlineStr"/>
+      <c r="C163" t="inlineStr"/>
+      <c r="D163" t="inlineStr"/>
+      <c r="E163" t="inlineStr"/>
+      <c r="F163" t="inlineStr"/>
+      <c r="G163" t="inlineStr"/>
+      <c r="H163" t="inlineStr"/>
+      <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr">
+        <is>
+          <t>4. Reload the page and click the same Left Column cell</t>
+        </is>
+      </c>
+      <c r="L163" t="inlineStr">
+        <is>
+          <t>All 300 characters are present — no truncation</t>
+        </is>
+      </c>
+      <c r="M163" t="inlineStr"/>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-053</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>Editor state isolation — switching from Left to Right Column shows correct content</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D163" t="inlineStr">
+      <c r="D164" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E163" t="inlineStr">
+      <c r="E164" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F163" t="inlineStr">
+      <c r="F164" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G163" t="inlineStr">
+      <c r="G164" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H163" t="inlineStr">
+      <c r="H164" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I163" t="inlineStr">
+      <c r="I164" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J163" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row with a known unique name exists.
+      <c r="J164" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row has distinct content in Left Column ("LEFT-CONTENT-A") and Right Column ("RIGHT-CONTENT-A").
 "": persistence</t>
         </is>
       </c>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>1. Click the Left Column cell of the target row</t>
-        </is>
-      </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>The editor opens</t>
-        </is>
-      </c>
-      <c r="M163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr"/>
-      <c r="B164" t="inlineStr"/>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-      <c r="E164" t="inlineStr"/>
-      <c r="F164" t="inlineStr"/>
-      <c r="G164" t="inlineStr"/>
-      <c r="H164" t="inlineStr"/>
-      <c r="I164" t="inlineStr"/>
-      <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr">
         <is>
-          <t>2. Clear existing content and type a 300-character string using keyboard</t>
+          <t>1. Click the Left Column cell</t>
         </is>
       </c>
       <c r="L164" t="inlineStr">
         <is>
-          <t>The editor shows all 300 characters</t>
+          <t>The editor shows "LEFT-CONTENT-A"</t>
         </is>
       </c>
       <c r="M164" t="inlineStr"/>
@@ -6536,12 +6540,12 @@
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr">
         <is>
-          <t>3. Click Save</t>
+          <t>2. Dismiss any unsaved-changes dialog if prompted (click Discard)</t>
         </is>
       </c>
       <c r="L165" t="inlineStr">
         <is>
-          <t>Save completes</t>
+          <t>Dialog dismissed</t>
         </is>
       </c>
       <c r="M165" t="inlineStr"/>
@@ -6559,12 +6563,12 @@
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr">
         <is>
-          <t>4. Reload the page and click the same Left Column cell</t>
+          <t>3. Click the Right Column cell</t>
         </is>
       </c>
       <c r="L166" t="inlineStr">
         <is>
-          <t>All 300 characters are present — no truncation</t>
+          <t>The editor shows "RIGHT-CONTENT-A" — no trace of Left Column content</t>
         </is>
       </c>
       <c r="M166" t="inlineStr"/>
@@ -6572,12 +6576,12 @@
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-054</t>
+          <t xml:space="preserve">TC-TNC-CORE-054</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>the HTML-entity-handling defect tooltip entity rendering (pending-probe)</t>
+          <t>Editor state isolation — switching between rows in the same column</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
@@ -6609,24 +6613,28 @@
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J167" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row contains &amp;nbsp; stored as &amp;amp;nbsp; in a column cell.
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). Row A and Row B have distinct content in the Left Column.
 "": persistence</t>
         </is>
       </c>
       <c r="K167" t="inlineStr">
         <is>
-          <t>1. Hover over the cell containing the stored &amp;amp;nbsp</t>
+          <t>1. Click Row A's Left Column cell</t>
         </is>
       </c>
       <c r="L167" t="inlineStr">
         <is>
-          <t>A tooltip appears</t>
+          <t>The editor shows Row A's Left Column content</t>
         </is>
       </c>
       <c r="M167" t="inlineStr"/>
@@ -6644,12 +6652,12 @@
       <c r="J168" t="inlineStr"/>
       <c r="K168" t="inlineStr">
         <is>
-          <t>2. content</t>
+          <t>2. Dismiss any unsaved-changes dialog (click Discard)</t>
         </is>
       </c>
       <c r="L168" t="inlineStr">
         <is>
-          <t>PENDING-PROBE: whether the tooltip shows literal `&amp;nbsp;` (escaped rendering) or a space (interpreted rendering) has not been measured</t>
+          <t>Dialog dismissed</t>
         </is>
       </c>
       <c r="M168" t="inlineStr"/>
@@ -6667,21 +6675,25 @@
       <c r="J169" t="inlineStr"/>
       <c r="K169" t="inlineStr">
         <is>
-          <t>3. Read the tooltip text</t>
-        </is>
-      </c>
-      <c r="L169" t="inlineStr"/>
+          <t>3. Click Row B's Left Column cell</t>
+        </is>
+      </c>
+      <c r="L169" t="inlineStr">
+        <is>
+          <t>The editor shows Row B's Left Column content — no trace of Row A</t>
+        </is>
+      </c>
       <c r="M169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-055</t>
+          <t xml:space="preserve">TC-TNC-CORE-055</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Editor state isolation — switching from Left to Right Column shows correct content</t>
+          <t>Editor state isolation — multi-cell alternation does not leak content</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
@@ -6723,18 +6735,18 @@
       </c>
       <c r="J170" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row has distinct content in Left Column ("LEFT-CONTENT-A") and Right Column ("RIGHT-CONTENT-A").
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). Three cells have distinct content: Row 1 Left ("AAA"), Row 1 Right ("BBB"), Row 2 Left ("CCC").
 "": persistence</t>
         </is>
       </c>
       <c r="K170" t="inlineStr">
         <is>
-          <t>1. Click the Left Column cell</t>
+          <t>1. Click Row 1 Left Column cell</t>
         </is>
       </c>
       <c r="L170" t="inlineStr">
         <is>
-          <t>The editor shows "LEFT-CONTENT-A"</t>
+          <t>Editor shows "AAA"</t>
         </is>
       </c>
       <c r="M170" t="inlineStr"/>
@@ -6752,12 +6764,12 @@
       <c r="J171" t="inlineStr"/>
       <c r="K171" t="inlineStr">
         <is>
-          <t>2. Dismiss any unsaved-changes dialog if prompted (click Discard)</t>
+          <t>2. Immediately click Row 1 Right Column cell (dismiss dialog if prompted)</t>
         </is>
       </c>
       <c r="L171" t="inlineStr">
         <is>
-          <t>Dialog dismissed</t>
+          <t>Editor shows "BBB"</t>
         </is>
       </c>
       <c r="M171" t="inlineStr"/>
@@ -6775,101 +6787,102 @@
       <c r="J172" t="inlineStr"/>
       <c r="K172" t="inlineStr">
         <is>
-          <t>3. Click the Right Column cell</t>
+          <t>3. Immediately click Row 2 Left Column cell (dismiss dialog if prompted)</t>
         </is>
       </c>
       <c r="L172" t="inlineStr">
         <is>
-          <t>The editor shows "RIGHT-CONTENT-A" — no trace of Left Column content</t>
+          <t>Editor shows "CCC"</t>
         </is>
       </c>
       <c r="M172" t="inlineStr"/>
     </row>
     <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-056</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Editor state isolation — switching between rows in the same column</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
+      <c r="A173" t="inlineStr"/>
+      <c r="B173" t="inlineStr"/>
+      <c r="C173" t="inlineStr"/>
+      <c r="D173" t="inlineStr"/>
+      <c r="E173" t="inlineStr"/>
+      <c r="F173" t="inlineStr"/>
+      <c r="G173" t="inlineStr"/>
+      <c r="H173" t="inlineStr"/>
+      <c r="I173" t="inlineStr"/>
+      <c r="J173" t="inlineStr"/>
+      <c r="K173" t="inlineStr">
+        <is>
+          <t>4. Click Row 1 Left Column cell again (dismiss dialog if prompted)</t>
+        </is>
+      </c>
+      <c r="L173" t="inlineStr">
+        <is>
+          <t>Editor shows "AAA" — no contamination from the rapid switching</t>
+        </is>
+      </c>
+      <c r="M173" t="inlineStr"/>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-056</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Content saved under one language does not alter another language's content</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr">
+      <c r="D174" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E173" t="inlineStr">
+      <c r="E174" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
+Application: Navigator
+Sample input 1: "ENGLISH-MODIFIED"</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G173" t="inlineStr">
+      <c r="G174" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H173" t="inlineStr">
+      <c r="H174" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I173" t="inlineStr">
+      <c r="I174" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J173" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). Row A and Row B have distinct content in the Left Column.
+      <c r="J174" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language filter: All. Two rows exist: Row A (US English, Left Column: "ENGLISH-CONTENT") and Row B (Spanish (Mexico), Left Column: "SPANISH-CONTENT").
 "": persistence</t>
         </is>
       </c>
-      <c r="K173" t="inlineStr">
-        <is>
-          <t>1. Click Row A's Left Column cell</t>
-        </is>
-      </c>
-      <c r="L173" t="inlineStr">
-        <is>
-          <t>The editor shows Row A's Left Column content</t>
-        </is>
-      </c>
-      <c r="M173" t="inlineStr"/>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr"/>
-      <c r="B174" t="inlineStr"/>
-      <c r="C174" t="inlineStr"/>
-      <c r="D174" t="inlineStr"/>
-      <c r="E174" t="inlineStr"/>
-      <c r="F174" t="inlineStr"/>
-      <c r="G174" t="inlineStr"/>
-      <c r="H174" t="inlineStr"/>
-      <c r="I174" t="inlineStr"/>
-      <c r="J174" t="inlineStr"/>
       <c r="K174" t="inlineStr">
         <is>
-          <t>2. Dismiss any unsaved-changes dialog (click Discard)</t>
+          <t>1. Click Row A's Left Column cell and change content to "ENGLISH-MODIFIED"</t>
         </is>
       </c>
       <c r="L174" t="inlineStr">
         <is>
-          <t>Dialog dismissed</t>
+          <t>Editor shows modified content</t>
         </is>
       </c>
       <c r="M174" t="inlineStr"/>
@@ -6887,78 +6900,35 @@
       <c r="J175" t="inlineStr"/>
       <c r="K175" t="inlineStr">
         <is>
-          <t>3. Click Row B's Left Column cell</t>
+          <t>2. Click Save</t>
         </is>
       </c>
       <c r="L175" t="inlineStr">
         <is>
-          <t>The editor shows Row B's Left Column content — no trace of Row A</t>
+          <t>Save completes</t>
         </is>
       </c>
       <c r="M175" t="inlineStr"/>
     </row>
     <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-057</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>Editor state isolation — multi-cell alternation does not leak content</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D176" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H176" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I176" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J176" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). Three cells have distinct content: Row 1 Left ("AAA"), Row 1 Right ("BBB"), Row 2 Left ("CCC").
-"": persistence</t>
-        </is>
-      </c>
+      <c r="A176" t="inlineStr"/>
+      <c r="B176" t="inlineStr"/>
+      <c r="C176" t="inlineStr"/>
+      <c r="D176" t="inlineStr"/>
+      <c r="E176" t="inlineStr"/>
+      <c r="F176" t="inlineStr"/>
+      <c r="G176" t="inlineStr"/>
+      <c r="H176" t="inlineStr"/>
+      <c r="I176" t="inlineStr"/>
+      <c r="J176" t="inlineStr"/>
       <c r="K176" t="inlineStr">
         <is>
-          <t>1. Click Row 1 Left Column cell</t>
+          <t>3. Reload the page with Language filter set to All</t>
         </is>
       </c>
       <c r="L176" t="inlineStr">
         <is>
-          <t>Editor shows "AAA"</t>
+          <t>Both rows visible</t>
         </is>
       </c>
       <c r="M176" t="inlineStr"/>
@@ -6976,35 +6946,80 @@
       <c r="J177" t="inlineStr"/>
       <c r="K177" t="inlineStr">
         <is>
-          <t>2. Immediately click Row 1 Right Column cell (dismiss dialog if prompted)</t>
+          <t>4. Click Row B's Left Column cell</t>
         </is>
       </c>
       <c r="L177" t="inlineStr">
         <is>
-          <t>Editor shows "BBB"</t>
+          <t>Editor shows "SPANISH-CONTENT" — unchanged by the English row edit</t>
         </is>
       </c>
       <c r="M177" t="inlineStr"/>
     </row>
     <row r="178">
-      <c r="A178" t="inlineStr"/>
-      <c r="B178" t="inlineStr"/>
-      <c r="C178" t="inlineStr"/>
-      <c r="D178" t="inlineStr"/>
-      <c r="E178" t="inlineStr"/>
-      <c r="F178" t="inlineStr"/>
-      <c r="G178" t="inlineStr"/>
-      <c r="H178" t="inlineStr"/>
-      <c r="I178" t="inlineStr"/>
-      <c r="J178" t="inlineStr"/>
+      <c r="A178" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-057</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Name uniqueness is enforced across languages</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>terms-conditions</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "SHARED-NAME-TEST"
+Sample input 2: "UNIQUE-SPANISH-NAME"</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H178" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I178" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="J178" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language filter: All. Row A (US English) has name "SHARED-NAME-TEST".
+"": persistence</t>
+        </is>
+      </c>
       <c r="K178" t="inlineStr">
         <is>
-          <t>3. Immediately click Row 2 Left Column cell (dismiss dialog if prompted)</t>
+          <t>1. Find or create a row with language Spanish (Mexico)</t>
         </is>
       </c>
       <c r="L178" t="inlineStr">
         <is>
-          <t>Editor shows "CCC"</t>
+          <t>The Spanish row is visible</t>
         </is>
       </c>
       <c r="M178" t="inlineStr"/>
@@ -7022,102 +7037,103 @@
       <c r="J179" t="inlineStr"/>
       <c r="K179" t="inlineStr">
         <is>
-          <t>4. Click Row 1 Left Column cell again (dismiss dialog if prompted)</t>
+          <t>2. Type "SHARED-NAME-TEST" into the Spanish row's Name field</t>
         </is>
       </c>
       <c r="L179" t="inlineStr">
         <is>
-          <t>Editor shows "AAA" — no contamination from the rapid switching</t>
+          <t>`aria-invalid="true"` appears on the input; Save remains disabled</t>
         </is>
       </c>
       <c r="M179" t="inlineStr"/>
     </row>
     <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-058</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Content saved under one language does not alter another language's content</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
+      <c r="A180" t="inlineStr"/>
+      <c r="B180" t="inlineStr"/>
+      <c r="C180" t="inlineStr"/>
+      <c r="D180" t="inlineStr"/>
+      <c r="E180" t="inlineStr"/>
+      <c r="F180" t="inlineStr"/>
+      <c r="G180" t="inlineStr"/>
+      <c r="H180" t="inlineStr"/>
+      <c r="I180" t="inlineStr"/>
+      <c r="J180" t="inlineStr"/>
+      <c r="K180" t="inlineStr">
+        <is>
+          <t>3. Change the Spanish row's name to "UNIQUE-SPANISH-NAME"</t>
+        </is>
+      </c>
+      <c r="L180" t="inlineStr">
+        <is>
+          <t>`aria-invalid` clears; Save becomes enabled (given the form is dirty)</t>
+        </is>
+      </c>
+      <c r="M180" t="inlineStr"/>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-058</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Multiple rows edited — single save commits all as a unit</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D180" t="inlineStr">
+      <c r="D181" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E180" t="inlineStr">
+      <c r="E181" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator
-Sample input 1: "ENGLISH-MODIFIED"</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
+Sample input 1: "BATCH-ROW-A-MODIFIED"
+Sample input 2: "BATCH-ROW-B-MODIFIED"</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G180" t="inlineStr">
+      <c r="G181" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H180" t="inlineStr">
+      <c r="H181" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I180" t="inlineStr">
+      <c r="I181" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J180" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language filter: All. Two rows exist: Row A (US English, Left Column: "ENGLISH-CONTENT") and Row B (Spanish (Mexico), Left Column: "SPANISH-CONTENT").
+      <c r="J181" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). Two rows with known unique names exist.
 "": persistence</t>
         </is>
       </c>
-      <c r="K180" t="inlineStr">
-        <is>
-          <t>1. Click Row A's Left Column cell and change content to "ENGLISH-MODIFIED"</t>
-        </is>
-      </c>
-      <c r="L180" t="inlineStr">
-        <is>
-          <t>Editor shows modified content</t>
-        </is>
-      </c>
-      <c r="M180" t="inlineStr"/>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr"/>
-      <c r="B181" t="inlineStr"/>
-      <c r="C181" t="inlineStr"/>
-      <c r="D181" t="inlineStr"/>
-      <c r="E181" t="inlineStr"/>
-      <c r="F181" t="inlineStr"/>
-      <c r="G181" t="inlineStr"/>
-      <c r="H181" t="inlineStr"/>
-      <c r="I181" t="inlineStr"/>
-      <c r="J181" t="inlineStr"/>
       <c r="K181" t="inlineStr">
         <is>
-          <t>2. Click Save</t>
+          <t>1. Change Row A's name to "BATCH-ROW-A-MODIFIED"</t>
         </is>
       </c>
       <c r="L181" t="inlineStr">
         <is>
-          <t>Save completes</t>
+          <t>Save becomes enabled</t>
         </is>
       </c>
       <c r="M181" t="inlineStr"/>
@@ -7135,12 +7151,12 @@
       <c r="J182" t="inlineStr"/>
       <c r="K182" t="inlineStr">
         <is>
-          <t>3. Reload the page with Language filter set to All</t>
+          <t>2. Change Row B's name to "BATCH-ROW-B-MODIFIED"</t>
         </is>
       </c>
       <c r="L182" t="inlineStr">
         <is>
-          <t>Both rows visible</t>
+          <t>Save stays enabled</t>
         </is>
       </c>
       <c r="M182" t="inlineStr"/>
@@ -7158,103 +7174,101 @@
       <c r="J183" t="inlineStr"/>
       <c r="K183" t="inlineStr">
         <is>
-          <t>4. Click Row B's Left Column cell</t>
+          <t>3. Click Save</t>
         </is>
       </c>
       <c r="L183" t="inlineStr">
         <is>
-          <t>Editor shows "SPANISH-CONTENT" — unchanged by the English row edit</t>
+          <t>Save completes — the save payload contains ALL rows</t>
         </is>
       </c>
       <c r="M183" t="inlineStr"/>
     </row>
     <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-059</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Name uniqueness is enforced across languages</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
+      <c r="A184" t="inlineStr"/>
+      <c r="B184" t="inlineStr"/>
+      <c r="C184" t="inlineStr"/>
+      <c r="D184" t="inlineStr"/>
+      <c r="E184" t="inlineStr"/>
+      <c r="F184" t="inlineStr"/>
+      <c r="G184" t="inlineStr"/>
+      <c r="H184" t="inlineStr"/>
+      <c r="I184" t="inlineStr"/>
+      <c r="J184" t="inlineStr"/>
+      <c r="K184" t="inlineStr">
+        <is>
+          <t>4. Reload the page</t>
+        </is>
+      </c>
+      <c r="L184" t="inlineStr">
+        <is>
+          <t>Both "BATCH-ROW-A-MODIFIED" and "BATCH-ROW-B-MODIFIED" are present</t>
+        </is>
+      </c>
+      <c r="M184" t="inlineStr"/>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-059</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Batch save persists language change</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr">
+      <c r="D185" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E184" t="inlineStr">
+      <c r="E185" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator
-Sample input 1: "SHARED-NAME-TEST"
-Sample input 2: "UNIQUE-SPANISH-NAME"</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G184" t="inlineStr">
+      <c r="G185" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H184" t="inlineStr">
+      <c r="H185" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I184" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="J184" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language filter: All. Row A (US English) has name "SHARED-NAME-TEST".
+      <c r="I185" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J185" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. The grid contains residue rows (rows with extreme content from prior automation runs).
 "": persistence</t>
         </is>
       </c>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>1. Find or create a row with language Spanish (Mexico)</t>
-        </is>
-      </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>The Spanish row is visible</t>
-        </is>
-      </c>
-      <c r="M184" t="inlineStr"/>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr"/>
-      <c r="B185" t="inlineStr"/>
-      <c r="C185" t="inlineStr"/>
-      <c r="D185" t="inlineStr"/>
-      <c r="E185" t="inlineStr"/>
-      <c r="F185" t="inlineStr"/>
-      <c r="G185" t="inlineStr"/>
-      <c r="H185" t="inlineStr"/>
-      <c r="I185" t="inlineStr"/>
-      <c r="J185" t="inlineStr"/>
       <c r="K185" t="inlineStr">
         <is>
-          <t>2. Type "SHARED-NAME-TEST" into the Spanish row's Name field</t>
+          <t>1. Change a clean row's language to a different value</t>
         </is>
       </c>
       <c r="L185" t="inlineStr">
         <is>
-          <t>`aria-invalid="true"` appears on the input; Save remains disabled</t>
+          <t>Save becomes enabled</t>
         </is>
       </c>
       <c r="M185" t="inlineStr"/>
@@ -7272,103 +7286,101 @@
       <c r="J186" t="inlineStr"/>
       <c r="K186" t="inlineStr">
         <is>
-          <t>3. Change the Spanish row's name to "UNIQUE-SPANISH-NAME"</t>
+          <t>2. Click Save and intercept the network response</t>
         </is>
       </c>
       <c r="L186" t="inlineStr">
         <is>
-          <t>`aria-invalid` clears; Save becomes enabled (given the form is dirty)</t>
+          <t>The server returns HTTP 500</t>
         </is>
       </c>
       <c r="M186" t="inlineStr"/>
     </row>
     <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-060</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Multiple rows edited — single save commits all as a unit</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
+      <c r="A187" t="inlineStr"/>
+      <c r="B187" t="inlineStr"/>
+      <c r="C187" t="inlineStr"/>
+      <c r="D187" t="inlineStr"/>
+      <c r="E187" t="inlineStr"/>
+      <c r="F187" t="inlineStr"/>
+      <c r="G187" t="inlineStr"/>
+      <c r="H187" t="inlineStr"/>
+      <c r="I187" t="inlineStr"/>
+      <c r="J187" t="inlineStr"/>
+      <c r="K187" t="inlineStr">
+        <is>
+          <t>3. Reload the page and verify the language change</t>
+        </is>
+      </c>
+      <c r="L187" t="inlineStr">
+        <is>
+          <t>The change is NOT persisted — entire batch discarded</t>
+        </is>
+      </c>
+      <c r="M187" t="inlineStr"/>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-060</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Save failure via route interception — form stays dirty, documenting a known application issue</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D187" t="inlineStr">
+      <c r="D188" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E187" t="inlineStr">
+      <c r="E188" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator
-Sample input 1: "BATCH-ROW-A-MODIFIED"
-Sample input 2: "BATCH-ROW-B-MODIFIED"</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G187" t="inlineStr">
+      <c r="G188" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H187" t="inlineStr">
+      <c r="H188" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I187" t="inlineStr">
+      <c r="I188" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J187" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). Two rows with known unique names exist.
+      <c r="J188" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). Network interception is configured to return HTTP 500 for the save endpoint.
 "": persistence</t>
         </is>
       </c>
-      <c r="K187" t="inlineStr">
-        <is>
-          <t>1. Change Row A's name to "BATCH-ROW-A-MODIFIED"</t>
-        </is>
-      </c>
-      <c r="L187" t="inlineStr">
+      <c r="K188" t="inlineStr">
+        <is>
+          <t>1. Change a row's name to trigger unsaved changes</t>
+        </is>
+      </c>
+      <c r="L188" t="inlineStr">
         <is>
           <t>Save becomes enabled</t>
-        </is>
-      </c>
-      <c r="M187" t="inlineStr"/>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr"/>
-      <c r="B188" t="inlineStr"/>
-      <c r="C188" t="inlineStr"/>
-      <c r="D188" t="inlineStr"/>
-      <c r="E188" t="inlineStr"/>
-      <c r="F188" t="inlineStr"/>
-      <c r="G188" t="inlineStr"/>
-      <c r="H188" t="inlineStr"/>
-      <c r="I188" t="inlineStr"/>
-      <c r="J188" t="inlineStr"/>
-      <c r="K188" t="inlineStr">
-        <is>
-          <t>2. Change Row B's name to "BATCH-ROW-B-MODIFIED"</t>
-        </is>
-      </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>Save stays enabled</t>
         </is>
       </c>
       <c r="M188" t="inlineStr"/>
@@ -7386,12 +7398,12 @@
       <c r="J189" t="inlineStr"/>
       <c r="K189" t="inlineStr">
         <is>
-          <t>3. Click Save</t>
+          <t>2. Click Save (intercepted to return 500)</t>
         </is>
       </c>
       <c r="L189" t="inlineStr">
         <is>
-          <t>Save completes — the save payload contains ALL rows</t>
+          <t>An error message appears (toast, banner, or inline) indicating save failed</t>
         </is>
       </c>
       <c r="M189" t="inlineStr"/>
@@ -7409,78 +7421,35 @@
       <c r="J190" t="inlineStr"/>
       <c r="K190" t="inlineStr">
         <is>
-          <t>4. Reload the page</t>
+          <t>3. Verify Save button state</t>
         </is>
       </c>
       <c r="L190" t="inlineStr">
         <is>
-          <t>Both "BATCH-ROW-A-MODIFIED" and "BATCH-ROW-B-MODIFIED" are present</t>
+          <t>Save remains enabled — the form stays dirty so the user can retry</t>
         </is>
       </c>
       <c r="M190" t="inlineStr"/>
     </row>
     <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-061</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Batch save persists language change</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D191" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H191" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I191" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J191" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. The grid contains residue rows (rows with extreme content from prior automation runs).
-"": persistence</t>
-        </is>
-      </c>
+      <c r="A191" t="inlineStr"/>
+      <c r="B191" t="inlineStr"/>
+      <c r="C191" t="inlineStr"/>
+      <c r="D191" t="inlineStr"/>
+      <c r="E191" t="inlineStr"/>
+      <c r="F191" t="inlineStr"/>
+      <c r="G191" t="inlineStr"/>
+      <c r="H191" t="inlineStr"/>
+      <c r="I191" t="inlineStr"/>
+      <c r="J191" t="inlineStr"/>
       <c r="K191" t="inlineStr">
         <is>
-          <t>1. Change a clean row's language to a different value</t>
+          <t>4. Remove the route interception</t>
         </is>
       </c>
       <c r="L191" t="inlineStr">
         <is>
-          <t>Save becomes enabled</t>
+          <t>Network restored</t>
         </is>
       </c>
       <c r="M191" t="inlineStr"/>
@@ -7498,101 +7467,101 @@
       <c r="J192" t="inlineStr"/>
       <c r="K192" t="inlineStr">
         <is>
-          <t>2. Click Save and intercept the network response</t>
+          <t>5. Click Save again</t>
         </is>
       </c>
       <c r="L192" t="inlineStr">
         <is>
-          <t>The server returns HTTP 500</t>
+          <t>Save succeeds (HTTP 2xx); the edit persists after reload</t>
         </is>
       </c>
       <c r="M192" t="inlineStr"/>
     </row>
     <row r="193">
-      <c r="A193" t="inlineStr"/>
-      <c r="B193" t="inlineStr"/>
-      <c r="C193" t="inlineStr"/>
-      <c r="D193" t="inlineStr"/>
-      <c r="E193" t="inlineStr"/>
-      <c r="F193" t="inlineStr"/>
-      <c r="G193" t="inlineStr"/>
-      <c r="H193" t="inlineStr"/>
-      <c r="I193" t="inlineStr"/>
-      <c r="J193" t="inlineStr"/>
-      <c r="K193" t="inlineStr">
-        <is>
-          <t>3. Reload the page and verify the language change</t>
-        </is>
-      </c>
-      <c r="L193" t="inlineStr">
-        <is>
-          <t>The change is NOT persisted — entire batch discarded</t>
-        </is>
-      </c>
-      <c r="M193" t="inlineStr"/>
-    </row>
-    <row r="194">
-      <c r="A194" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-062</t>
-        </is>
-      </c>
-      <c r="B194" t="inlineStr">
-        <is>
-          <t>Save failure via route interception — form stays dirty, documenting a known application issue</t>
-        </is>
-      </c>
-      <c r="C194" t="inlineStr">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-061</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Name field — 1 character minimum positive</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D194" t="inlineStr">
+      <c r="D193" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E194" t="inlineStr">
+      <c r="E193" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F194" t="inlineStr">
+Application: Navigator
+Sample input 1: "X"</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G194" t="inlineStr">
+      <c r="G193" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H194" t="inlineStr">
+      <c r="H193" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I194" t="inlineStr">
+      <c r="I193" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J194" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). Network interception is configured to return HTTP 500 for the save endpoint.
-"": persistence</t>
-        </is>
-      </c>
+      <c r="J193" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
+        </is>
+      </c>
+      <c r="K193" t="inlineStr">
+        <is>
+          <t>1. Clear a row's Name field and type a single unique character "X"</t>
+        </is>
+      </c>
+      <c r="L193" t="inlineStr">
+        <is>
+          <t>`aria-invalid` is false; Save becomes enabled</t>
+        </is>
+      </c>
+      <c r="M193" t="inlineStr"/>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr"/>
+      <c r="B194" t="inlineStr"/>
+      <c r="C194" t="inlineStr"/>
+      <c r="D194" t="inlineStr"/>
+      <c r="E194" t="inlineStr"/>
+      <c r="F194" t="inlineStr"/>
+      <c r="G194" t="inlineStr"/>
+      <c r="H194" t="inlineStr"/>
+      <c r="I194" t="inlineStr"/>
+      <c r="J194" t="inlineStr"/>
       <c r="K194" t="inlineStr">
         <is>
-          <t>1. Change a row's name to trigger unsaved changes</t>
+          <t>2. Click Save</t>
         </is>
       </c>
       <c r="L194" t="inlineStr">
         <is>
-          <t>Save becomes enabled</t>
+          <t>Save completes</t>
         </is>
       </c>
       <c r="M194" t="inlineStr"/>
@@ -7610,35 +7579,77 @@
       <c r="J195" t="inlineStr"/>
       <c r="K195" t="inlineStr">
         <is>
-          <t>2. Click Save (intercepted to return 500)</t>
+          <t>3. Reload the page</t>
         </is>
       </c>
       <c r="L195" t="inlineStr">
         <is>
-          <t>An error message appears (toast, banner, or inline) indicating save failed</t>
+          <t>The name "X" persists on the row</t>
         </is>
       </c>
       <c r="M195" t="inlineStr"/>
     </row>
     <row r="196">
-      <c r="A196" t="inlineStr"/>
-      <c r="B196" t="inlineStr"/>
-      <c r="C196" t="inlineStr"/>
-      <c r="D196" t="inlineStr"/>
-      <c r="E196" t="inlineStr"/>
-      <c r="F196" t="inlineStr"/>
-      <c r="G196" t="inlineStr"/>
-      <c r="H196" t="inlineStr"/>
-      <c r="I196" t="inlineStr"/>
-      <c r="J196" t="inlineStr"/>
+      <c r="A196" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-062</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>Name field — 260 characters accepted</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>terms-conditions</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G196" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H196" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I196" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="J196" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
+        </is>
+      </c>
       <c r="K196" t="inlineStr">
         <is>
-          <t>3. Verify Save button state</t>
+          <t>1. Clear a row's Name field and type a 260-character unique string</t>
         </is>
       </c>
       <c r="L196" t="inlineStr">
         <is>
-          <t>Save remains enabled — the form stays dirty so the user can retry</t>
+          <t>`aria-invalid` is false; Save becomes enabled; no truncation</t>
         </is>
       </c>
       <c r="M196" t="inlineStr"/>
@@ -7656,12 +7667,12 @@
       <c r="J197" t="inlineStr"/>
       <c r="K197" t="inlineStr">
         <is>
-          <t>4. Remove the route interception</t>
+          <t>2. Click Save</t>
         </is>
       </c>
       <c r="L197" t="inlineStr">
         <is>
-          <t>Network restored</t>
+          <t>Save completes</t>
         </is>
       </c>
       <c r="M197" t="inlineStr"/>
@@ -7679,12 +7690,12 @@
       <c r="J198" t="inlineStr"/>
       <c r="K198" t="inlineStr">
         <is>
-          <t>5. Click Save again</t>
+          <t>3. Reload the page</t>
         </is>
       </c>
       <c r="L198" t="inlineStr">
         <is>
-          <t>Save succeeds (HTTP 2xx); the edit persists after reload</t>
+          <t>All 260 characters persist without truncation</t>
         </is>
       </c>
       <c r="M198" t="inlineStr"/>
@@ -7692,12 +7703,12 @@
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-063</t>
+          <t xml:space="preserve">TC-TNC-CORE-063</t>
         </is>
       </c>
       <c r="B199" t="inlineStr">
         <is>
-          <t>Name field — 1 character minimum positive</t>
+          <t>Name field — empty triggers red border and blocks Save</t>
         </is>
       </c>
       <c r="C199" t="inlineStr">
@@ -7714,8 +7725,7 @@
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator
-Sample input 1: "X"</t>
+Application: Navigator</t>
         </is>
       </c>
       <c r="F199" t="inlineStr">
@@ -7740,17 +7750,17 @@
       </c>
       <c r="J199" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row has an existing name</t>
         </is>
       </c>
       <c r="K199" t="inlineStr">
         <is>
-          <t>1. Clear a row's Name field and type a single unique character "X"</t>
+          <t>1. Clear the row's Name field entirely</t>
         </is>
       </c>
       <c r="L199" t="inlineStr">
         <is>
-          <t>`aria-invalid` is false; Save becomes enabled</t>
+          <t>`aria-invalid="true"` appears; border color changes to red-orange (oklch(0.577 0.245 27.325)); Save becomes disabled</t>
         </is>
       </c>
       <c r="M199" t="inlineStr"/>
@@ -7768,123 +7778,166 @@
       <c r="J200" t="inlineStr"/>
       <c r="K200" t="inlineStr">
         <is>
-          <t>2. Click Save</t>
+          <t>2. Attempt to Tab away from the field</t>
         </is>
       </c>
       <c r="L200" t="inlineStr">
         <is>
-          <t>Save completes</t>
+          <t>Focus moves — the field does not trap focus (escapable per the field-validation rules)</t>
         </is>
       </c>
       <c r="M200" t="inlineStr"/>
     </row>
     <row r="201">
-      <c r="A201" t="inlineStr"/>
-      <c r="B201" t="inlineStr"/>
-      <c r="C201" t="inlineStr"/>
-      <c r="D201" t="inlineStr"/>
-      <c r="E201" t="inlineStr"/>
-      <c r="F201" t="inlineStr"/>
-      <c r="G201" t="inlineStr"/>
-      <c r="H201" t="inlineStr"/>
-      <c r="I201" t="inlineStr"/>
-      <c r="J201" t="inlineStr"/>
-      <c r="K201" t="inlineStr">
-        <is>
-          <t>3. Reload the page</t>
-        </is>
-      </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>The name "X" persists on the row</t>
-        </is>
-      </c>
-      <c r="M201" t="inlineStr"/>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-064</t>
-        </is>
-      </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>Name field — 260 characters accepted</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-064</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Name field — whitespace-only triggers silent block</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr">
+      <c r="D201" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E202" t="inlineStr">
+      <c r="E201" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F202" t="inlineStr">
+      <c r="F201" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G202" t="inlineStr">
+      <c r="G201" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H202" t="inlineStr">
+      <c r="H201" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I202" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="J202" t="inlineStr">
+      <c r="I201" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J201" t="inlineStr">
         <is>
           <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
         </is>
       </c>
+      <c r="K201" t="inlineStr">
+        <is>
+          <t>1. Clear a row's Name field and type three spaces</t>
+        </is>
+      </c>
+      <c r="L201" t="inlineStr">
+        <is>
+          <t>`aria-invalid="true"` appears; Save is disabled</t>
+        </is>
+      </c>
+      <c r="M201" t="inlineStr"/>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr"/>
+      <c r="B202" t="inlineStr"/>
+      <c r="C202" t="inlineStr"/>
+      <c r="D202" t="inlineStr"/>
+      <c r="E202" t="inlineStr"/>
+      <c r="F202" t="inlineStr"/>
+      <c r="G202" t="inlineStr"/>
+      <c r="H202" t="inlineStr"/>
+      <c r="I202" t="inlineStr"/>
+      <c r="J202" t="inlineStr"/>
       <c r="K202" t="inlineStr">
         <is>
-          <t>1. Clear a row's Name field and type a 260-character unique string</t>
+          <t>2. Attempt to Tab away from the field</t>
         </is>
       </c>
       <c r="L202" t="inlineStr">
         <is>
-          <t>`aria-invalid` is false; Save becomes enabled; no truncation</t>
+          <t>Focus moves — not trapped</t>
         </is>
       </c>
       <c r="M202" t="inlineStr"/>
     </row>
     <row r="203">
-      <c r="A203" t="inlineStr"/>
-      <c r="B203" t="inlineStr"/>
-      <c r="C203" t="inlineStr"/>
-      <c r="D203" t="inlineStr"/>
-      <c r="E203" t="inlineStr"/>
-      <c r="F203" t="inlineStr"/>
-      <c r="G203" t="inlineStr"/>
-      <c r="H203" t="inlineStr"/>
-      <c r="I203" t="inlineStr"/>
-      <c r="J203" t="inlineStr"/>
+      <c r="A203" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-065</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Name field — duplicate name triggers silent block</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>terms-conditions</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator
+Sample input 1: "EXISTING-NAME"</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G203" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H203" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I203" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J203" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). An existing row has name "EXISTING-NAME"</t>
+        </is>
+      </c>
       <c r="K203" t="inlineStr">
         <is>
-          <t>2. Click Save</t>
+          <t>1. Change a different row's Name to "EXISTING-NAME"</t>
         </is>
       </c>
       <c r="L203" t="inlineStr">
         <is>
-          <t>Save completes</t>
+          <t>`aria-invalid="true"` appears; Save is disabled; NO visible error message or tooltip</t>
         </is>
       </c>
       <c r="M203" t="inlineStr"/>
@@ -7902,12 +7955,12 @@
       <c r="J204" t="inlineStr"/>
       <c r="K204" t="inlineStr">
         <is>
-          <t>3. Reload the page</t>
+          <t>2. Attempt to Tab away from the field</t>
         </is>
       </c>
       <c r="L204" t="inlineStr">
         <is>
-          <t>All 260 characters persist without truncation</t>
+          <t>Focus moves — not trapped</t>
         </is>
       </c>
       <c r="M204" t="inlineStr"/>
@@ -7915,12 +7968,12 @@
     <row r="205">
       <c r="A205" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-065</t>
+          <t xml:space="preserve">TC-TNC-CORE-066</t>
         </is>
       </c>
       <c r="B205" t="inlineStr">
         <is>
-          <t>Name field — empty triggers red border and blocks Save</t>
+          <t>Name field — special characters persist byte-exact</t>
         </is>
       </c>
       <c r="C205" t="inlineStr">
@@ -7962,17 +8015,17 @@
       </c>
       <c r="J205" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row has an existing name</t>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
         </is>
       </c>
       <c r="K205" t="inlineStr">
         <is>
-          <t>1. Clear the row's Name field entirely</t>
+          <t>1. Clear a row's Name field and type &lt; &gt; &amp; " ' / \ % # Cafe Nono 中文</t>
         </is>
       </c>
       <c r="L205" t="inlineStr">
         <is>
-          <t>`aria-invalid="true"` appears; border color changes to red-orange (oklch(0.577 0.245 27.325)); Save becomes disabled</t>
+          <t>`aria-invalid` is false; Save becomes enabled</t>
         </is>
       </c>
       <c r="M205" t="inlineStr"/>
@@ -7990,277 +8043,279 @@
       <c r="J206" t="inlineStr"/>
       <c r="K206" t="inlineStr">
         <is>
-          <t>2. Attempt to Tab away from the field</t>
+          <t>2. Click Save</t>
         </is>
       </c>
       <c r="L206" t="inlineStr">
         <is>
-          <t>Focus moves — the field does not trap focus (escapable per the field-validation rules)</t>
+          <t>Save completes</t>
         </is>
       </c>
       <c r="M206" t="inlineStr"/>
     </row>
     <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-066</t>
-        </is>
-      </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>Name field — whitespace-only triggers silent block</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
+      <c r="A207" t="inlineStr"/>
+      <c r="B207" t="inlineStr"/>
+      <c r="C207" t="inlineStr"/>
+      <c r="D207" t="inlineStr"/>
+      <c r="E207" t="inlineStr"/>
+      <c r="F207" t="inlineStr"/>
+      <c r="G207" t="inlineStr"/>
+      <c r="H207" t="inlineStr"/>
+      <c r="I207" t="inlineStr"/>
+      <c r="J207" t="inlineStr"/>
+      <c r="K207" t="inlineStr">
+        <is>
+          <t>3. Reload the page</t>
+        </is>
+      </c>
+      <c r="L207" t="inlineStr">
+        <is>
+          <t>The name field shows the exact string including all special and non-ASCII characters</t>
+        </is>
+      </c>
+      <c r="M207" t="inlineStr"/>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-067</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>State transition — Clean to Dirty via name edit</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D207" t="inlineStr">
+      <c r="D208" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E207" t="inlineStr">
+      <c r="E208" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F207" t="inlineStr">
+      <c r="F208" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G207" t="inlineStr">
+      <c r="G208" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H207" t="inlineStr">
+      <c r="H208" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I207" t="inlineStr">
+      <c r="I208" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J207" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
-        </is>
-      </c>
-      <c r="K207" t="inlineStr">
-        <is>
-          <t>1. Clear a row's Name field and type three spaces</t>
-        </is>
-      </c>
-      <c r="L207" t="inlineStr">
-        <is>
-          <t>`aria-invalid="true"` appears; Save is disabled</t>
-        </is>
-      </c>
-      <c r="M207" t="inlineStr"/>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr"/>
-      <c r="B208" t="inlineStr"/>
-      <c r="C208" t="inlineStr"/>
-      <c r="D208" t="inlineStr"/>
-      <c r="E208" t="inlineStr"/>
-      <c r="F208" t="inlineStr"/>
-      <c r="G208" t="inlineStr"/>
-      <c r="H208" t="inlineStr"/>
-      <c r="I208" t="inlineStr"/>
-      <c r="J208" t="inlineStr"/>
+      <c r="J208" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). No pending edits (Save is disabled).
+"": persistence</t>
+        </is>
+      </c>
       <c r="K208" t="inlineStr">
         <is>
-          <t>2. Attempt to Tab away from the field</t>
+          <t>1. Verify Save is disabled (Clean state)</t>
         </is>
       </c>
       <c r="L208" t="inlineStr">
         <is>
-          <t>Focus moves — not trapped</t>
+          <t>Save button has `disabled` attribute</t>
         </is>
       </c>
       <c r="M208" t="inlineStr"/>
     </row>
     <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-067</t>
-        </is>
-      </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>Name field — duplicate name triggers silent block</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
+      <c r="A209" t="inlineStr"/>
+      <c r="B209" t="inlineStr"/>
+      <c r="C209" t="inlineStr"/>
+      <c r="D209" t="inlineStr"/>
+      <c r="E209" t="inlineStr"/>
+      <c r="F209" t="inlineStr"/>
+      <c r="G209" t="inlineStr"/>
+      <c r="H209" t="inlineStr"/>
+      <c r="I209" t="inlineStr"/>
+      <c r="J209" t="inlineStr"/>
+      <c r="K209" t="inlineStr">
+        <is>
+          <t>2. Type a character into a row's Name field</t>
+        </is>
+      </c>
+      <c r="L209" t="inlineStr">
+        <is>
+          <t>Save becomes enabled (transition to Dirty)</t>
+        </is>
+      </c>
+      <c r="M209" t="inlineStr"/>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-068</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>State transition — Clean to Dirty via language change</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D209" t="inlineStr">
+      <c r="D210" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E209" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "EXISTING-NAME"</t>
-        </is>
-      </c>
-      <c r="F209" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G209" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H209" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I209" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J209" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). An existing row has name "EXISTING-NAME"</t>
-        </is>
-      </c>
-      <c r="K209" t="inlineStr">
-        <is>
-          <t>1. Change a different row's Name to "EXISTING-NAME"</t>
-        </is>
-      </c>
-      <c r="L209" t="inlineStr">
-        <is>
-          <t>`aria-invalid="true"` appears; Save is disabled; NO visible error message or tooltip</t>
-        </is>
-      </c>
-      <c r="M209" t="inlineStr"/>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr"/>
-      <c r="B210" t="inlineStr"/>
-      <c r="C210" t="inlineStr"/>
-      <c r="D210" t="inlineStr"/>
-      <c r="E210" t="inlineStr"/>
-      <c r="F210" t="inlineStr"/>
-      <c r="G210" t="inlineStr"/>
-      <c r="H210" t="inlineStr"/>
-      <c r="I210" t="inlineStr"/>
-      <c r="J210" t="inlineStr"/>
-      <c r="K210" t="inlineStr">
-        <is>
-          <t>2. Attempt to Tab away from the field</t>
-        </is>
-      </c>
-      <c r="L210" t="inlineStr">
-        <is>
-          <t>Focus moves — not trapped</t>
-        </is>
-      </c>
-      <c r="M210" t="inlineStr"/>
-    </row>
-    <row r="211">
-      <c r="A211" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-068</t>
-        </is>
-      </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>Name field — special characters persist byte-exact</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E211" t="inlineStr">
+      <c r="E210" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F211" t="inlineStr">
+      <c r="F210" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G211" t="inlineStr">
+      <c r="G210" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H211" t="inlineStr">
+      <c r="H210" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I211" t="inlineStr">
+      <c r="I210" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J211" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
-        </is>
-      </c>
+      <c r="J210" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). No pending edits.
+"": persistence</t>
+        </is>
+      </c>
+      <c r="K210" t="inlineStr">
+        <is>
+          <t>1. Verify Save is disabled (Clean state)</t>
+        </is>
+      </c>
+      <c r="L210" t="inlineStr">
+        <is>
+          <t>Save button has `disabled` attribute</t>
+        </is>
+      </c>
+      <c r="M210" t="inlineStr"/>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr"/>
+      <c r="B211" t="inlineStr"/>
+      <c r="C211" t="inlineStr"/>
+      <c r="D211" t="inlineStr"/>
+      <c r="E211" t="inlineStr"/>
+      <c r="F211" t="inlineStr"/>
+      <c r="G211" t="inlineStr"/>
+      <c r="H211" t="inlineStr"/>
+      <c r="I211" t="inlineStr"/>
+      <c r="J211" t="inlineStr"/>
       <c r="K211" t="inlineStr">
         <is>
-          <t>1. Clear a row's Name field and type &lt; &gt; &amp; " ' / \ % # Cafe Nono 中文</t>
+          <t>2. Change a row's language dropdown to a different value</t>
         </is>
       </c>
       <c r="L211" t="inlineStr">
         <is>
-          <t>`aria-invalid` is false; Save becomes enabled</t>
+          <t>Save becomes enabled (transition to Dirty)</t>
         </is>
       </c>
       <c r="M211" t="inlineStr"/>
     </row>
     <row r="212">
-      <c r="A212" t="inlineStr"/>
-      <c r="B212" t="inlineStr"/>
-      <c r="C212" t="inlineStr"/>
-      <c r="D212" t="inlineStr"/>
-      <c r="E212" t="inlineStr"/>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr"/>
-      <c r="H212" t="inlineStr"/>
-      <c r="I212" t="inlineStr"/>
-      <c r="J212" t="inlineStr"/>
+      <c r="A212" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-069</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>State transition — Dirty to Saving to Save-OK</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>terms-conditions</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>core</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>User: automation user (location-edit permission)
+Location: test office 1604
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="G212" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="H212" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I212" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J212" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. The form is dirty (Save enabled). Network interception captures the save response.
+"": persistence</t>
+        </is>
+      </c>
       <c r="K212" t="inlineStr">
         <is>
-          <t>2. Click Save</t>
+          <t>1. Click Save</t>
         </is>
       </c>
       <c r="L212" t="inlineStr">
         <is>
-          <t>Save completes</t>
+          <t>The save request fires; Save transitions to disabled during the request</t>
         </is>
       </c>
       <c r="M212" t="inlineStr"/>
@@ -8278,117 +8333,101 @@
       <c r="J213" t="inlineStr"/>
       <c r="K213" t="inlineStr">
         <is>
-          <t>3. Reload the page</t>
+          <t>2. Observe the network response</t>
         </is>
       </c>
       <c r="L213" t="inlineStr">
         <is>
-          <t>The name field shows the exact string including all special and non-ASCII characters</t>
+          <t>HTTP 2xx returned</t>
         </is>
       </c>
       <c r="M213" t="inlineStr"/>
     </row>
     <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-069</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>Pairwise covering array - language x row-position x column-type x data-state</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
+      <c r="A214" t="inlineStr"/>
+      <c r="B214" t="inlineStr"/>
+      <c r="C214" t="inlineStr"/>
+      <c r="D214" t="inlineStr"/>
+      <c r="E214" t="inlineStr"/>
+      <c r="F214" t="inlineStr"/>
+      <c r="G214" t="inlineStr"/>
+      <c r="H214" t="inlineStr"/>
+      <c r="I214" t="inlineStr"/>
+      <c r="J214" t="inlineStr"/>
+      <c r="K214" t="inlineStr">
+        <is>
+          <t>3. Verify post-save state</t>
+        </is>
+      </c>
+      <c r="L214" t="inlineStr">
+        <is>
+          <t>Save is disabled (Clean state restored); page is at rest</t>
+        </is>
+      </c>
+      <c r="M214" t="inlineStr"/>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-070</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>State transition — Dirty to Save-Failed</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D214" t="inlineStr">
+      <c r="D215" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E214" t="inlineStr">
+      <c r="E215" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F214" t="inlineStr">
+      <c r="F215" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G214" t="inlineStr">
+      <c r="G215" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I214" t="inlineStr"/>
-      <c r="J214" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language filter: All. At least 4 rows present spanning at least 2 languages.
-"": persistence
-"Pairwise factors:"
-- Language (L): {US English, Spanish (Mexico), English (Canada), French (Canada)} - 4 levels
-- Row position (R): {first, middle, last} - 3 levels
-- Column type (C): {Name (plain text), Left (HTML/RTE), Right (HTML/RTE), Bottom (HTML/RTE)} - 4 levels
-- Data state (D): {new-fill, existing-edit, empty/cleared} - 3 levels
-"Covering array (all pairs present, 12 trials - cap at 12; see dropped-pairs below):"
-| Trial | Language | Row | Column | Data State |
-|---|---|---|---|---|
-| 1 | US English | first | Name | new-fill |
-| 2 | US English | middle | Left | existing-edit |
-| 3 | US English | last | Right | empty/cleared |
-| 4 | Spanish (Mexico) | first | Left | empty/cleared |
-| 5 | Spanish (Mexico) | middle | Right | new-fill |
-| 6 | Spanish (Mexico) | last | Name | existing-edit |
-| 7 | English (Canada) | first | Right | existing-edit |
-| 8 | English (Canada) | middle | Bottom | empty/cleared |
-| 9 | English (Canada) | last | Name | new-fill |
-| 10 | French (Canada) | first | Bottom | new-fill |
-| 11 | French (Canada) | middle | Name | empty/cleared |
-| 12 | French (Canada) | last | Left | existing-edit</t>
-        </is>
-      </c>
-      <c r="K214" t="inlineStr">
-        <is>
-          <t>1. For each trial 1-12: navigate to the specified row (by position anchor), target the specified column, apply the specified data state operation</t>
-        </is>
-      </c>
-      <c r="L214" t="inlineStr">
-        <is>
-          <t>The edit succeeds without error for valid operations; invalid states (empty Name) show `aria-invalid`</t>
-        </is>
-      </c>
-      <c r="M214" t="inlineStr"/>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr"/>
-      <c r="B215" t="inlineStr"/>
-      <c r="C215" t="inlineStr"/>
-      <c r="D215" t="inlineStr"/>
-      <c r="E215" t="inlineStr"/>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr"/>
-      <c r="H215" t="inlineStr"/>
-      <c r="I215" t="inlineStr"/>
-      <c r="J215" t="inlineStr"/>
+      <c r="H215" t="inlineStr">
+        <is>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I215" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J215" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. The form is dirty. Network interception configured to return HTTP 500.
+"": persistence</t>
+        </is>
+      </c>
       <c r="K215" t="inlineStr">
         <is>
-          <t>2. Click Save after all 12 trials are applied</t>
+          <t>1. Click Save (intercepted to return 500)</t>
         </is>
       </c>
       <c r="L215" t="inlineStr">
         <is>
-          <t>Save completes for valid edits</t>
+          <t>The save request fires</t>
         </is>
       </c>
       <c r="M215" t="inlineStr"/>
@@ -8406,12 +8445,12 @@
       <c r="J216" t="inlineStr"/>
       <c r="K216" t="inlineStr">
         <is>
-          <t>3. Reload the page and verify each trial's result persists</t>
+          <t>2. Verify post-failure state</t>
         </is>
       </c>
       <c r="L216" t="inlineStr">
         <is>
-          <t>Each valid edit persists; empty Name edits blocked Save and did not persist</t>
+          <t>Save should remain enabled (form stays Dirty); an error message should appear</t>
         </is>
       </c>
       <c r="M216" t="inlineStr"/>
@@ -8419,12 +8458,12 @@
     <row r="217">
       <c r="A217" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-070</t>
+          <t xml:space="preserve">TC-TNC-CORE-071</t>
         </is>
       </c>
       <c r="B217" t="inlineStr">
         <is>
-          <t>State transition — Clean to Dirty via name edit</t>
+          <t>State transition — Dirty triggers beforeunload on navigate away</t>
         </is>
       </c>
       <c r="C217" t="inlineStr">
@@ -8466,18 +8505,18 @@
       </c>
       <c r="J217" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). No pending edits (Save is disabled).
+          <t>The Terms and Conditions page is open for office 1604. The form is dirty.
 "": persistence</t>
         </is>
       </c>
       <c r="K217" t="inlineStr">
         <is>
-          <t>1. Verify Save is disabled (Clean state)</t>
+          <t>1. Attempt to navigate away (e.g., click browser back or navigate to a different URL)</t>
         </is>
       </c>
       <c r="L217" t="inlineStr">
         <is>
-          <t>Save button has `disabled` attribute</t>
+          <t>The native `beforeunload` dialog fires</t>
         </is>
       </c>
       <c r="M217" t="inlineStr"/>
@@ -8495,12 +8534,12 @@
       <c r="J218" t="inlineStr"/>
       <c r="K218" t="inlineStr">
         <is>
-          <t>2. Type a character into a row's Name field</t>
+          <t>2. Cancel the navigation (Stay)</t>
         </is>
       </c>
       <c r="L218" t="inlineStr">
         <is>
-          <t>Save becomes enabled (transition to Dirty)</t>
+          <t>The page remains; form is still dirty; Save still enabled</t>
         </is>
       </c>
       <c r="M218" t="inlineStr"/>
@@ -8508,12 +8547,12 @@
     <row r="219">
       <c r="A219" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-071</t>
+          <t xml:space="preserve">TC-TNC-CORE-072</t>
         </is>
       </c>
       <c r="B219" t="inlineStr">
         <is>
-          <t>State transition — Clean to Dirty via language change</t>
+          <t>State transition — Language filter change on dirty form raises guard (Stay)</t>
         </is>
       </c>
       <c r="C219" t="inlineStr">
@@ -8555,18 +8594,18 @@
       </c>
       <c r="J219" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). No pending edits.
+          <t>The Terms and Conditions page is open for office 1604. The form is dirty.
 "": persistence</t>
         </is>
       </c>
       <c r="K219" t="inlineStr">
         <is>
-          <t>1. Verify Save is disabled (Clean state)</t>
+          <t>1. Click the Language filter and select a different option</t>
         </is>
       </c>
       <c r="L219" t="inlineStr">
         <is>
-          <t>Save button has `disabled` attribute</t>
+          <t>The warning dialog opens with title "Unsaved changes" and body "Are you sure you want to leave this view? Any unsaved changes will be lost."</t>
         </is>
       </c>
       <c r="M219" t="inlineStr"/>
@@ -8584,12 +8623,12 @@
       <c r="J220" t="inlineStr"/>
       <c r="K220" t="inlineStr">
         <is>
-          <t>2. Change a row's language dropdown to a different value</t>
+          <t>2. Click Stay</t>
         </is>
       </c>
       <c r="L220" t="inlineStr">
         <is>
-          <t>Save becomes enabled (transition to Dirty)</t>
+          <t>The dialog dismisses; form remains dirty; Save still enabled; filter unchanged</t>
         </is>
       </c>
       <c r="M220" t="inlineStr"/>
@@ -8597,12 +8636,12 @@
     <row r="221">
       <c r="A221" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-072</t>
+          <t xml:space="preserve">TC-TNC-CORE-073</t>
         </is>
       </c>
       <c r="B221" t="inlineStr">
         <is>
-          <t>State transition - Clean to Dirty (RTE edit)</t>
+          <t>State transition — Language filter change on dirty form (Discard)</t>
         </is>
       </c>
       <c r="C221" t="inlineStr">
@@ -8634,24 +8673,28 @@
       </c>
       <c r="H221" t="inlineStr">
         <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I221" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I221" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J221" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). No pending edits.
+          <t>The Terms and Conditions page is open for office 1604. The form is dirty.
 "": persistence</t>
         </is>
       </c>
       <c r="K221" t="inlineStr">
         <is>
-          <t>1. Verify Save is disabled (Clean state)</t>
+          <t>1. Click the Language filter and select a different option</t>
         </is>
       </c>
       <c r="L221" t="inlineStr">
         <is>
-          <t>Save button has `disabled` attribute</t>
+          <t>The warning dialog opens</t>
         </is>
       </c>
       <c r="M221" t="inlineStr"/>
@@ -8669,12 +8712,12 @@
       <c r="J222" t="inlineStr"/>
       <c r="K222" t="inlineStr">
         <is>
-          <t>2. Click a Left Column cell and type content</t>
+          <t>2. Click Discard</t>
         </is>
       </c>
       <c r="L222" t="inlineStr">
         <is>
-          <t>Save becomes enabled (transition to Dirty)</t>
+          <t>The dialog dismisses; edits are discarded; grid reloads with the new filter; Save is disabled (Clean)</t>
         </is>
       </c>
       <c r="M222" t="inlineStr"/>
@@ -8682,12 +8725,12 @@
     <row r="223">
       <c r="A223" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-073</t>
+          <t xml:space="preserve">TC-TNC-CORE-074</t>
         </is>
       </c>
       <c r="B223" t="inlineStr">
         <is>
-          <t>State transition — Dirty to Saving to Save-OK</t>
+          <t>No guard dialog when editing a different row while one is dirty (NM-2191 gap)</t>
         </is>
       </c>
       <c r="C223" t="inlineStr">
@@ -8729,18 +8772,18 @@
       </c>
       <c r="J223" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. The form is dirty (Save enabled). Network interception captures the save response.
+          <t>The Terms and Conditions page is open for office 1604. Row A's name has been edited (form is dirty). Row B is visible.
 "": persistence</t>
         </is>
       </c>
       <c r="K223" t="inlineStr">
         <is>
-          <t>1. Click Save</t>
+          <t>1. Click Row B's Name input</t>
         </is>
       </c>
       <c r="L223" t="inlineStr">
         <is>
-          <t>The save request fires; Save transitions to disabled during the request</t>
+          <t>Focus moves to Row B; NO guard dialog fires</t>
         </is>
       </c>
       <c r="M223" t="inlineStr"/>
@@ -8758,279 +8801,282 @@
       <c r="J224" t="inlineStr"/>
       <c r="K224" t="inlineStr">
         <is>
-          <t>2. Observe the network response</t>
+          <t>2. Edit Row B's name</t>
         </is>
       </c>
       <c r="L224" t="inlineStr">
         <is>
-          <t>HTTP 2xx returned</t>
+          <t>Both rows are now dirty; no warning was shown at any point</t>
         </is>
       </c>
       <c r="M224" t="inlineStr"/>
     </row>
     <row r="225">
-      <c r="A225" t="inlineStr"/>
-      <c r="B225" t="inlineStr"/>
-      <c r="C225" t="inlineStr"/>
-      <c r="D225" t="inlineStr"/>
-      <c r="E225" t="inlineStr"/>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr"/>
-      <c r="H225" t="inlineStr"/>
-      <c r="I225" t="inlineStr"/>
-      <c r="J225" t="inlineStr"/>
-      <c r="K225" t="inlineStr">
-        <is>
-          <t>3. Verify post-save state</t>
-        </is>
-      </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>Save is disabled (Clean state restored); page is at rest</t>
-        </is>
-      </c>
-      <c r="M225" t="inlineStr"/>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-074</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>State transition — Dirty to Save-Failed</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
+      <c r="A225" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-075</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>Validation-Error to Fix returns to Dirty</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D226" t="inlineStr">
+      <c r="D225" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E226" t="inlineStr">
+      <c r="E225" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F226" t="inlineStr">
+      <c r="F225" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G226" t="inlineStr">
+      <c r="G225" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H226" t="inlineStr">
+      <c r="H225" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I226" t="inlineStr">
+      <c r="I225" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J226" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. The form is dirty. Network interception configured to return HTTP 500.
+      <c r="J225" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. A row's Name is in validation error state (e.g., duplicate or empty).
 "": persistence</t>
         </is>
       </c>
+      <c r="K225" t="inlineStr">
+        <is>
+          <t>1. Verify Save is disabled and input shows a validation error</t>
+        </is>
+      </c>
+      <c r="L225" t="inlineStr">
+        <is>
+          <t>Validation error state confirmed</t>
+        </is>
+      </c>
+      <c r="M225" t="inlineStr"/>
+    </row>
+    <row r="226">
+      <c r="A226" t="inlineStr"/>
+      <c r="B226" t="inlineStr"/>
+      <c r="C226" t="inlineStr"/>
+      <c r="D226" t="inlineStr"/>
+      <c r="E226" t="inlineStr"/>
+      <c r="F226" t="inlineStr"/>
+      <c r="G226" t="inlineStr"/>
+      <c r="H226" t="inlineStr"/>
+      <c r="I226" t="inlineStr"/>
+      <c r="J226" t="inlineStr"/>
       <c r="K226" t="inlineStr">
         <is>
-          <t>1. Click Save (intercepted to return 500)</t>
+          <t>2. Fix the name (type a unique, non-empty value)</t>
         </is>
       </c>
       <c r="L226" t="inlineStr">
         <is>
-          <t>The save request fires</t>
+          <t>`aria-invalid` clears; Save becomes enabled because the corrected name is an unsaved change</t>
         </is>
       </c>
       <c r="M226" t="inlineStr"/>
     </row>
     <row r="227">
-      <c r="A227" t="inlineStr"/>
-      <c r="B227" t="inlineStr"/>
-      <c r="C227" t="inlineStr"/>
-      <c r="D227" t="inlineStr"/>
-      <c r="E227" t="inlineStr"/>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr"/>
-      <c r="H227" t="inlineStr"/>
-      <c r="I227" t="inlineStr"/>
-      <c r="J227" t="inlineStr"/>
-      <c r="K227" t="inlineStr">
-        <is>
-          <t>2. Verify post-failure state</t>
-        </is>
-      </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>Save should remain enabled (form stays Dirty); an error message should appear</t>
-        </is>
-      </c>
-      <c r="M227" t="inlineStr"/>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-075</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>State transition — Dirty triggers beforeunload on navigate away</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
+      <c r="A227" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-076</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
+        <is>
+          <t>Reverting edit to original value disables Save</t>
+        </is>
+      </c>
+      <c r="C227" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D228" t="inlineStr">
+      <c r="D227" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E228" t="inlineStr">
+      <c r="E227" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr">
+Application: Navigator
+Sample input 1: "TEMP-DIFFERENT"
+Sample input 2: "ORIGINAL-NAME"</t>
+        </is>
+      </c>
+      <c r="F227" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G228" t="inlineStr">
+      <c r="G227" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H228" t="inlineStr">
+      <c r="H227" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I228" t="inlineStr">
+      <c r="I227" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J228" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. The form is dirty.
+      <c r="J227" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. A row has saved name "ORIGINAL-NAME".
 "": persistence</t>
         </is>
       </c>
+      <c r="K227" t="inlineStr">
+        <is>
+          <t>1. Change the row's name to "TEMP-DIFFERENT"</t>
+        </is>
+      </c>
+      <c r="L227" t="inlineStr">
+        <is>
+          <t>Save becomes enabled (Dirty)</t>
+        </is>
+      </c>
+      <c r="M227" t="inlineStr"/>
+    </row>
+    <row r="228">
+      <c r="A228" t="inlineStr"/>
+      <c r="B228" t="inlineStr"/>
+      <c r="C228" t="inlineStr"/>
+      <c r="D228" t="inlineStr"/>
+      <c r="E228" t="inlineStr"/>
+      <c r="F228" t="inlineStr"/>
+      <c r="G228" t="inlineStr"/>
+      <c r="H228" t="inlineStr"/>
+      <c r="I228" t="inlineStr"/>
+      <c r="J228" t="inlineStr"/>
       <c r="K228" t="inlineStr">
         <is>
-          <t>1. Attempt to navigate away (e.g., click browser back or navigate to a different URL)</t>
+          <t>2. Change the name back to "ORIGINAL-NAME"</t>
         </is>
       </c>
       <c r="L228" t="inlineStr">
         <is>
-          <t>The native `beforeunload` dialog fires</t>
+          <t>Save becomes disabled — the form detects revert-to-original and returns to Clean</t>
         </is>
       </c>
       <c r="M228" t="inlineStr"/>
     </row>
     <row r="229">
-      <c r="A229" t="inlineStr"/>
-      <c r="B229" t="inlineStr"/>
-      <c r="C229" t="inlineStr"/>
-      <c r="D229" t="inlineStr"/>
-      <c r="E229" t="inlineStr"/>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr"/>
-      <c r="H229" t="inlineStr"/>
-      <c r="I229" t="inlineStr"/>
-      <c r="J229" t="inlineStr"/>
-      <c r="K229" t="inlineStr">
-        <is>
-          <t>2. Cancel the navigation (Stay)</t>
-        </is>
-      </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>The page remains; form is still dirty; Save still enabled</t>
-        </is>
-      </c>
-      <c r="M229" t="inlineStr"/>
-    </row>
-    <row r="230">
-      <c r="A230" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-076</t>
-        </is>
-      </c>
-      <c r="B230" t="inlineStr">
-        <is>
-          <t>State transition — Language filter change on dirty form raises guard (Stay)</t>
-        </is>
-      </c>
-      <c r="C230" t="inlineStr">
+      <c r="A229" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-077</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>Integration — Legal T&amp;C selection surfaces in Location Management History (NM-1200)</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D230" t="inlineStr">
+      <c r="D229" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E230" t="inlineStr">
+      <c r="E229" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F230" t="inlineStr">
+Application: Navigator
+Sample input 1: "HISTORY-TRACE-SENTINEL"</t>
+        </is>
+      </c>
+      <c r="F229" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G230" t="inlineStr">
+      <c r="G229" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H230" t="inlineStr">
+      <c r="H229" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I230" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J230" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. The form is dirty.
+      <c r="I229" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="J229" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A unique sentinel name is prepared for tracing.
 "": persistence</t>
         </is>
       </c>
+      <c r="K229" t="inlineStr">
+        <is>
+          <t>1. Change a row's name to a unique sentinel value (e.g., "HISTORY-TRACE-SENTINEL") and Save</t>
+        </is>
+      </c>
+      <c r="L229" t="inlineStr">
+        <is>
+          <t>Save completes</t>
+        </is>
+      </c>
+      <c r="M229" t="inlineStr"/>
+    </row>
+    <row r="230">
+      <c r="A230" t="inlineStr"/>
+      <c r="B230" t="inlineStr"/>
+      <c r="C230" t="inlineStr"/>
+      <c r="D230" t="inlineStr"/>
+      <c r="E230" t="inlineStr"/>
+      <c r="F230" t="inlineStr"/>
+      <c r="G230" t="inlineStr"/>
+      <c r="H230" t="inlineStr"/>
+      <c r="I230" t="inlineStr"/>
+      <c r="J230" t="inlineStr"/>
       <c r="K230" t="inlineStr">
         <is>
-          <t>1. Click the Language filter and select a different option</t>
+          <t>2. Navigate to Location Management History for office 1604</t>
         </is>
       </c>
       <c r="L230" t="inlineStr">
         <is>
-          <t>The warning dialog opens with title "Unsaved changes" and body "Are you sure you want to leave this view? Any unsaved changes will be lost."</t>
+          <t>The History page loads (reuse `the Location Management History page object`)</t>
         </is>
       </c>
       <c r="M230" t="inlineStr"/>
@@ -9048,12 +9094,12 @@
       <c r="J231" t="inlineStr"/>
       <c r="K231" t="inlineStr">
         <is>
-          <t>2. Click Stay</t>
+          <t>3. Search or filter for the most recent entry</t>
         </is>
       </c>
       <c r="L231" t="inlineStr">
         <is>
-          <t>The dialog dismisses; form remains dirty; Save still enabled; filter unchanged</t>
+          <t>A history row referencing the Terms and Conditions change is visible</t>
         </is>
       </c>
       <c r="M231" t="inlineStr"/>
@@ -9061,12 +9107,12 @@
     <row r="232">
       <c r="A232" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-077</t>
+          <t xml:space="preserve">TC-TNC-CORE-078</t>
         </is>
       </c>
       <c r="B232" t="inlineStr">
         <is>
-          <t>State transition — Language filter change on dirty form (Discard)</t>
+          <t>Integration — T&amp;C required per language on Legal tab (NM-825/NM-664)</t>
         </is>
       </c>
       <c r="C232" t="inlineStr">
@@ -9108,18 +9154,18 @@
       </c>
       <c r="J232" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. The form is dirty.
+          <t>The Terms and Conditions page is open for office 1604. T&amp;C entries exist for at least two languages.
 "": persistence</t>
         </is>
       </c>
       <c r="K232" t="inlineStr">
         <is>
-          <t>1. Click the Language filter and select a different option</t>
+          <t>1. Navigate to the Legal tab for office 1604</t>
         </is>
       </c>
       <c r="L232" t="inlineStr">
         <is>
-          <t>The warning dialog opens</t>
+          <t>The Legal tab loads (reuse `the Location Legal page object`)</t>
         </is>
       </c>
       <c r="M232" t="inlineStr"/>
@@ -9137,12 +9183,12 @@
       <c r="J233" t="inlineStr"/>
       <c r="K233" t="inlineStr">
         <is>
-          <t>2. Click Discard</t>
+          <t>2. Verify T&amp;C information is reflected per language</t>
         </is>
       </c>
       <c r="L233" t="inlineStr">
         <is>
-          <t>The dialog dismisses; edits are discarded; grid reloads with the new filter; Save is disabled (Clean)</t>
+          <t>Language-specific T&amp;C content appears on the Legal tab</t>
         </is>
       </c>
       <c r="M233" t="inlineStr"/>
@@ -9150,12 +9196,12 @@
     <row r="234">
       <c r="A234" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-078</t>
+          <t xml:space="preserve">TC-TNC-CORE-079</t>
         </is>
       </c>
       <c r="B234" t="inlineStr">
         <is>
-          <t>No guard dialog when editing a different row while one is dirty (NM-2191 gap)</t>
+          <t>Error-guessing — double-click race on Save button</t>
         </is>
       </c>
       <c r="C234" t="inlineStr">
@@ -9197,18 +9243,17 @@
       </c>
       <c r="J234" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. Row A's name has been edited (form is dirty). Row B is visible.
-"": persistence</t>
+          <t>The Terms and Conditions page is open for office 1604. The form is dirty (Save enabled)</t>
         </is>
       </c>
       <c r="K234" t="inlineStr">
         <is>
-          <t>1. Click Row B's Name input</t>
+          <t>1. Rapidly double-click the Save button</t>
         </is>
       </c>
       <c r="L234" t="inlineStr">
         <is>
-          <t>Focus moves to Row B; NO guard dialog fires</t>
+          <t>Only one save request fires; Save disables after the first click; no duplicate submission</t>
         </is>
       </c>
       <c r="M234" t="inlineStr"/>
@@ -9226,12 +9271,12 @@
       <c r="J235" t="inlineStr"/>
       <c r="K235" t="inlineStr">
         <is>
-          <t>2. Edit Row B's name</t>
+          <t>2. Verify no duplicate network requests</t>
         </is>
       </c>
       <c r="L235" t="inlineStr">
         <is>
-          <t>Both rows are now dirty; no warning was shown at any point</t>
+          <t>Exactly one a save request to the server captured</t>
         </is>
       </c>
       <c r="M235" t="inlineStr"/>
@@ -9239,12 +9284,12 @@
     <row r="236">
       <c r="A236" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-079</t>
+          <t xml:space="preserve">TC-TNC-CORE-080</t>
         </is>
       </c>
       <c r="B236" t="inlineStr">
         <is>
-          <t>Validation-Error to Fix returns to Dirty</t>
+          <t>Error-guessing — save-failure retry succeeds after interception removed</t>
         </is>
       </c>
       <c r="C236" t="inlineStr">
@@ -9286,18 +9331,17 @@
       </c>
       <c r="J236" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. A row's Name is in validation error state (e.g., duplicate or empty).
-"": persistence</t>
+          <t>The Terms and Conditions page is open for office 1604. The form is dirty. First save will fail (route interception returns 500), then interception is removed</t>
         </is>
       </c>
       <c r="K236" t="inlineStr">
         <is>
-          <t>1. Verify Save is disabled and input shows a validation error</t>
+          <t>1. Click Save (intercepted: 500 returned)</t>
         </is>
       </c>
       <c r="L236" t="inlineStr">
         <is>
-          <t>Validation error state confirmed</t>
+          <t>Save should stay enabled for retry (correct expectation)</t>
         </is>
       </c>
       <c r="M236" t="inlineStr"/>
@@ -9315,12 +9359,12 @@
       <c r="J237" t="inlineStr"/>
       <c r="K237" t="inlineStr">
         <is>
-          <t>2. Fix the name (type a unique, non-empty value)</t>
+          <t>2. Remove interception and click Save again</t>
         </is>
       </c>
       <c r="L237" t="inlineStr">
         <is>
-          <t>`aria-invalid` clears; Save becomes enabled because the corrected name is an unsaved change</t>
+          <t>Save should succeed; edit persists after reload</t>
         </is>
       </c>
       <c r="M237" t="inlineStr"/>
@@ -9328,12 +9372,12 @@
     <row r="238">
       <c r="A238" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-080</t>
+          <t xml:space="preserve">TC-TNC-CORE-081</t>
         </is>
       </c>
       <c r="B238" t="inlineStr">
         <is>
-          <t>Reverting edit to original value disables Save</t>
+          <t>Error-guessing — language switched mid-RTE-edit</t>
         </is>
       </c>
       <c r="C238" t="inlineStr">
@@ -9350,9 +9394,7 @@
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator
-Sample input 1: "TEMP-DIFFERENT"
-Sample input 2: "ORIGINAL-NAME"</t>
+Application: Navigator</t>
         </is>
       </c>
       <c r="F238" t="inlineStr">
@@ -9377,18 +9419,17 @@
       </c>
       <c r="J238" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. A row has saved name "ORIGINAL-NAME".
-"": persistence</t>
+          <t>The Terms and Conditions page is open for office 1604. The editor is open with unsaved content in a row's Left Column</t>
         </is>
       </c>
       <c r="K238" t="inlineStr">
         <is>
-          <t>1. Change the row's name to "TEMP-DIFFERENT"</t>
+          <t>1. While the editor has unsaved content, change the same row's language dropdown</t>
         </is>
       </c>
       <c r="L238" t="inlineStr">
         <is>
-          <t>Save becomes enabled (Dirty)</t>
+          <t>The unsaved-changes guard fires (for the language filter change path) OR the language change applies without losing the RTE edit (for the per-row dropdown)</t>
         </is>
       </c>
       <c r="M238" t="inlineStr"/>
@@ -9406,12 +9447,12 @@
       <c r="J239" t="inlineStr"/>
       <c r="K239" t="inlineStr">
         <is>
-          <t>2. Change the name back to "ORIGINAL-NAME"</t>
+          <t>2. Click Save if enabled</t>
         </is>
       </c>
       <c r="L239" t="inlineStr">
         <is>
-          <t>Save becomes disabled — the form detects revert-to-original and returns to Clean</t>
+          <t>Both the language change and the RTE content persist</t>
         </is>
       </c>
       <c r="M239" t="inlineStr"/>
@@ -9419,12 +9460,12 @@
     <row r="240">
       <c r="A240" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-081</t>
+          <t xml:space="preserve">TC-TNC-CORE-082</t>
         </is>
       </c>
       <c r="B240" t="inlineStr">
         <is>
-          <t>State transition - Tab-to-tab navigation guard (unconfirmed)</t>
+          <t>Error-guessing — browser-back after successful save</t>
         </is>
       </c>
       <c r="C240" t="inlineStr">
@@ -9456,114 +9497,115 @@
       </c>
       <c r="H240" t="inlineStr">
         <is>
-          <t>Pending Automation</t>
-        </is>
-      </c>
-      <c r="I240" t="inlineStr"/>
+          <t>Automated</t>
+        </is>
+      </c>
+      <c r="I240" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
       <c r="J240" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. The form is dirty. A sibling settings tab link is visible.
-"": persistence</t>
+          <t>The Terms and Conditions page is open for office 1604. A save was just completed successfully (form is Clean)</t>
         </is>
       </c>
       <c r="K240" t="inlineStr">
         <is>
-          <t>1. Click a sibling settings tab (if one exists)</t>
+          <t>1. Click browser Back</t>
         </is>
       </c>
       <c r="L240" t="inlineStr">
         <is>
-          <t>UNCONFIRMED — whether a guard dialog fires on tab-to-tab navigation has not been tested (no tab link found in any probe)</t>
+          <t>Navigation proceeds without any `beforeunload` dialog (form is Clean)</t>
         </is>
       </c>
       <c r="M240" t="inlineStr"/>
     </row>
     <row r="241">
-      <c r="A241" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-082</t>
-        </is>
-      </c>
-      <c r="B241" t="inlineStr">
-        <is>
-          <t>Integration — Legal T&amp;C selection surfaces in Location Management History (NM-1200)</t>
-        </is>
-      </c>
-      <c r="C241" t="inlineStr">
+      <c r="A241" t="inlineStr"/>
+      <c r="B241" t="inlineStr"/>
+      <c r="C241" t="inlineStr"/>
+      <c r="D241" t="inlineStr"/>
+      <c r="E241" t="inlineStr"/>
+      <c r="F241" t="inlineStr"/>
+      <c r="G241" t="inlineStr"/>
+      <c r="H241" t="inlineStr"/>
+      <c r="I241" t="inlineStr"/>
+      <c r="J241" t="inlineStr"/>
+      <c r="K241" t="inlineStr">
+        <is>
+          <t>2. Click browser Forward to return</t>
+        </is>
+      </c>
+      <c r="L241" t="inlineStr">
+        <is>
+          <t>The T&amp;C page reloads with the saved data intact</t>
+        </is>
+      </c>
+      <c r="M241" t="inlineStr"/>
+    </row>
+    <row r="242">
+      <c r="A242" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-083</t>
+        </is>
+      </c>
+      <c r="B242" t="inlineStr">
+        <is>
+          <t>Accessibility — logical tab order through page controls</t>
+        </is>
+      </c>
+      <c r="C242" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D241" t="inlineStr">
+      <c r="D242" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E241" t="inlineStr">
+      <c r="E242" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator
-Sample input 1: "HISTORY-TRACE-SENTINEL"</t>
-        </is>
-      </c>
-      <c r="F241" t="inlineStr">
+Application: Navigator</t>
+        </is>
+      </c>
+      <c r="F242" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G241" t="inlineStr">
+      <c r="G242" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H241" t="inlineStr">
+      <c r="H242" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I241" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="J241" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A unique sentinel name is prepared for tracing.
-"": persistence</t>
-        </is>
-      </c>
-      <c r="K241" t="inlineStr">
-        <is>
-          <t>1. Change a row's name to a unique sentinel value (e.g., "HISTORY-TRACE-SENTINEL") and Save</t>
-        </is>
-      </c>
-      <c r="L241" t="inlineStr">
-        <is>
-          <t>Save completes</t>
-        </is>
-      </c>
-      <c r="M241" t="inlineStr"/>
-    </row>
-    <row r="242">
-      <c r="A242" t="inlineStr"/>
-      <c r="B242" t="inlineStr"/>
-      <c r="C242" t="inlineStr"/>
-      <c r="D242" t="inlineStr"/>
-      <c r="E242" t="inlineStr"/>
-      <c r="F242" t="inlineStr"/>
-      <c r="G242" t="inlineStr"/>
-      <c r="H242" t="inlineStr"/>
-      <c r="I242" t="inlineStr"/>
-      <c r="J242" t="inlineStr"/>
+      <c r="I242" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="J242" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
+        </is>
+      </c>
       <c r="K242" t="inlineStr">
         <is>
-          <t>2. Navigate to Location Management History for office 1604</t>
+          <t>1. Press Tab repeatedly from the first focusable element</t>
         </is>
       </c>
       <c r="L242" t="inlineStr">
         <is>
-          <t>The History page loads (reuse `the Location Management History page object`)</t>
+          <t>Focus moves in a logical order through: Language filter, grid rows (Language dropdown, Name input, column cells), Add row button, Save button</t>
         </is>
       </c>
       <c r="M242" t="inlineStr"/>
@@ -9581,12 +9623,12 @@
       <c r="J243" t="inlineStr"/>
       <c r="K243" t="inlineStr">
         <is>
-          <t>3. Search or filter for the most recent entry</t>
+          <t>2. Verify no focus skips or traps</t>
         </is>
       </c>
       <c r="L243" t="inlineStr">
         <is>
-          <t>A history row referencing the Terms and Conditions change is visible</t>
+          <t>Every interactive control is reachable via Tab; no element traps focus indefinitely</t>
         </is>
       </c>
       <c r="M243" t="inlineStr"/>
@@ -9594,12 +9636,12 @@
     <row r="244">
       <c r="A244" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-083</t>
+          <t xml:space="preserve">TC-TNC-CORE-084</t>
         </is>
       </c>
       <c r="B244" t="inlineStr">
         <is>
-          <t>Integration — T&amp;C required per language on Legal tab (NM-825/NM-664)</t>
+          <t>Accessibility — RTE keyboard operability</t>
         </is>
       </c>
       <c r="C244" t="inlineStr">
@@ -9636,23 +9678,22 @@
       </c>
       <c r="I244" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Skipped</t>
         </is>
       </c>
       <c r="J244" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. T&amp;C entries exist for at least two languages.
-"": persistence</t>
+          <t>The Terms and Conditions page is open for office 1604. A Left Column cell is visible</t>
         </is>
       </c>
       <c r="K244" t="inlineStr">
         <is>
-          <t>1. Navigate to the Legal tab for office 1604</t>
+          <t>1. Tab into the Left Column cell (or activate it via Enter/Space on the launcher button)</t>
         </is>
       </c>
       <c r="L244" t="inlineStr">
         <is>
-          <t>The Legal tab loads (reuse `the Location Legal page object`)</t>
+          <t>The RTE gains focus — the cursor is inside the contenteditable</t>
         </is>
       </c>
       <c r="M244" t="inlineStr"/>
@@ -9670,165 +9711,123 @@
       <c r="J245" t="inlineStr"/>
       <c r="K245" t="inlineStr">
         <is>
-          <t>2. Verify T&amp;C information is reflected per language</t>
+          <t>2. Type text using the keyboard</t>
         </is>
       </c>
       <c r="L245" t="inlineStr">
         <is>
-          <t>Language-specific T&amp;C content appears on the Legal tab</t>
+          <t>Characters appear in the editor</t>
         </is>
       </c>
       <c r="M245" t="inlineStr"/>
     </row>
     <row r="246">
-      <c r="A246" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-084</t>
-        </is>
-      </c>
-      <c r="B246" t="inlineStr">
-        <is>
-          <t>Error-guessing — double-click race on Save button</t>
-        </is>
-      </c>
-      <c r="C246" t="inlineStr">
+      <c r="A246" t="inlineStr"/>
+      <c r="B246" t="inlineStr"/>
+      <c r="C246" t="inlineStr"/>
+      <c r="D246" t="inlineStr"/>
+      <c r="E246" t="inlineStr"/>
+      <c r="F246" t="inlineStr"/>
+      <c r="G246" t="inlineStr"/>
+      <c r="H246" t="inlineStr"/>
+      <c r="I246" t="inlineStr"/>
+      <c r="J246" t="inlineStr"/>
+      <c r="K246" t="inlineStr">
+        <is>
+          <t>3. Press Tab or Escape to exit the editor</t>
+        </is>
+      </c>
+      <c r="L246" t="inlineStr">
+        <is>
+          <t>Focus moves OUT of the contenteditable to the next focusable element — the editor does not trap keyboard focus</t>
+        </is>
+      </c>
+      <c r="M246" t="inlineStr"/>
+    </row>
+    <row r="247">
+      <c r="A247" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-085</t>
+        </is>
+      </c>
+      <c r="B247" t="inlineStr">
+        <is>
+          <t>Accessibility — unsaved-changes dialog focus trap and restore</t>
+        </is>
+      </c>
+      <c r="C247" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr">
+      <c r="D247" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E246" t="inlineStr">
+      <c r="E247" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F246" t="inlineStr">
+      <c r="F247" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G246" t="inlineStr">
+      <c r="G247" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H246" t="inlineStr">
+      <c r="H247" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I246" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J246" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. The form is dirty (Save enabled)</t>
-        </is>
-      </c>
-      <c r="K246" t="inlineStr">
-        <is>
-          <t>1. Rapidly double-click the Save button</t>
-        </is>
-      </c>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t>Only one save request fires; Save disables after the first click; no duplicate submission</t>
-        </is>
-      </c>
-      <c r="M246" t="inlineStr"/>
-    </row>
-    <row r="247">
-      <c r="A247" t="inlineStr"/>
-      <c r="B247" t="inlineStr"/>
-      <c r="C247" t="inlineStr"/>
-      <c r="D247" t="inlineStr"/>
-      <c r="E247" t="inlineStr"/>
-      <c r="F247" t="inlineStr"/>
-      <c r="G247" t="inlineStr"/>
-      <c r="H247" t="inlineStr"/>
-      <c r="I247" t="inlineStr"/>
-      <c r="J247" t="inlineStr"/>
+      <c r="I247" t="inlineStr">
+        <is>
+          <t>Skipped</t>
+        </is>
+      </c>
+      <c r="J247" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. The form is dirty. The language filter is about to be changed (triggers the guard dialog)</t>
+        </is>
+      </c>
       <c r="K247" t="inlineStr">
         <is>
-          <t>2. Verify no duplicate network requests</t>
+          <t>1. Select a language filter option to trigger the guard dialog</t>
         </is>
       </c>
       <c r="L247" t="inlineStr">
         <is>
-          <t>Exactly one a save request to the server captured</t>
+          <t>The warning dialog appears; keyboard focus moves into it (accessibility focus behavior)</t>
         </is>
       </c>
       <c r="M247" t="inlineStr"/>
     </row>
     <row r="248">
-      <c r="A248" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-085</t>
-        </is>
-      </c>
-      <c r="B248" t="inlineStr">
-        <is>
-          <t>Error-guessing — save-failure retry succeeds after interception removed</t>
-        </is>
-      </c>
-      <c r="C248" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D248" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E248" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F248" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G248" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H248" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I248" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J248" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. The form is dirty. First save will fail (route interception returns 500), then interception is removed</t>
-        </is>
-      </c>
+      <c r="A248" t="inlineStr"/>
+      <c r="B248" t="inlineStr"/>
+      <c r="C248" t="inlineStr"/>
+      <c r="D248" t="inlineStr"/>
+      <c r="E248" t="inlineStr"/>
+      <c r="F248" t="inlineStr"/>
+      <c r="G248" t="inlineStr"/>
+      <c r="H248" t="inlineStr"/>
+      <c r="I248" t="inlineStr"/>
+      <c r="J248" t="inlineStr"/>
       <c r="K248" t="inlineStr">
         <is>
-          <t>1. Click Save (intercepted: 500 returned)</t>
+          <t>2. Press Tab within the dialog</t>
         </is>
       </c>
       <c r="L248" t="inlineStr">
         <is>
-          <t>Save should stay enabled for retry (correct expectation)</t>
+          <t>Focus cycles between Stay and Discard buttons (focus trapped within dialog)</t>
         </is>
       </c>
       <c r="M248" t="inlineStr"/>
@@ -9846,12 +9845,12 @@
       <c r="J249" t="inlineStr"/>
       <c r="K249" t="inlineStr">
         <is>
-          <t>2. Remove interception and click Save again</t>
+          <t>3. Press Escape or click Stay</t>
         </is>
       </c>
       <c r="L249" t="inlineStr">
         <is>
-          <t>Save should succeed; edit persists after reload</t>
+          <t>The dialog closes; focus returns to the element that triggered the dialog (the language filter)</t>
         </is>
       </c>
       <c r="M249" t="inlineStr"/>
@@ -9859,12 +9858,12 @@
     <row r="250">
       <c r="A250" t="inlineStr">
         <is>
-          <t>TC-TNC-CORE-086</t>
+          <t xml:space="preserve">TC-TNC-CORE-086</t>
         </is>
       </c>
       <c r="B250" t="inlineStr">
         <is>
-          <t>Error-guessing — language switched mid-RTE-edit</t>
+          <t>Network payload — PUT response body reflects committed data</t>
         </is>
       </c>
       <c r="C250" t="inlineStr">
@@ -9881,7 +9880,9 @@
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
-Application: Navigator</t>
+Application: Navigator
+Sample input 1: "NET-PAYLOAD-TEST"
+Sample input 2: "PAYLOAD-CONTENT"</t>
         </is>
       </c>
       <c r="F250" t="inlineStr">
@@ -9906,17 +9907,18 @@
       </c>
       <c r="J250" t="inlineStr">
         <is>
-          <t>The Terms and Conditions page is open for office 1604. The editor is open with unsaved content in a row's Left Column</t>
+          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row has been edited with a known Name and known RTE content. Network interception captures request and response.
+"": persistence</t>
         </is>
       </c>
       <c r="K250" t="inlineStr">
         <is>
-          <t>1. While the editor has unsaved content, change the same row's language dropdown</t>
+          <t>1. Edit a row: set Name to "NET-PAYLOAD-TEST", type "PAYLOAD-CONTENT" into Left Column</t>
         </is>
       </c>
       <c r="L250" t="inlineStr">
         <is>
-          <t>The unsaved-changes guard fires (for the language filter change path) OR the language change applies without losing the RTE edit (for the per-row dropdown)</t>
+          <t>Save becomes enabled</t>
         </is>
       </c>
       <c r="M250" t="inlineStr"/>
@@ -9934,165 +9936,124 @@
       <c r="J251" t="inlineStr"/>
       <c r="K251" t="inlineStr">
         <is>
-          <t>2. Click Save if enabled</t>
+          <t>2. Click Save and capture the save request payload</t>
         </is>
       </c>
       <c r="L251" t="inlineStr">
         <is>
-          <t>Both the language change and the RTE content persist</t>
+          <t>The request body contains: the edited row with `"languageId":"en-US"`, the name "NET-PAYLOAD-TEST", and the RTE content (HTML-escaped)</t>
         </is>
       </c>
       <c r="M251" t="inlineStr"/>
     </row>
     <row r="252">
-      <c r="A252" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-087</t>
-        </is>
-      </c>
-      <c r="B252" t="inlineStr">
-        <is>
-          <t>Error-guessing — browser-back after successful save</t>
-        </is>
-      </c>
-      <c r="C252" t="inlineStr">
+      <c r="A252" t="inlineStr"/>
+      <c r="B252" t="inlineStr"/>
+      <c r="C252" t="inlineStr"/>
+      <c r="D252" t="inlineStr"/>
+      <c r="E252" t="inlineStr"/>
+      <c r="F252" t="inlineStr"/>
+      <c r="G252" t="inlineStr"/>
+      <c r="H252" t="inlineStr"/>
+      <c r="I252" t="inlineStr"/>
+      <c r="J252" t="inlineStr"/>
+      <c r="K252" t="inlineStr">
+        <is>
+          <t>3. Capture the response body</t>
+        </is>
+      </c>
+      <c r="L252" t="inlineStr">
+        <is>
+          <t>The response reflects the committed payload — the saved row data appears in the response with matching `languageId`, name, and content</t>
+        </is>
+      </c>
+      <c r="M252" t="inlineStr"/>
+    </row>
+    <row r="253">
+      <c r="A253" t="inlineStr">
+        <is>
+          <t xml:space="preserve">TC-TNC-CORE-087</t>
+        </is>
+      </c>
+      <c r="B253" t="inlineStr">
+        <is>
+          <t>Volume — all rows render in one scroll view without pagination</t>
+        </is>
+      </c>
+      <c r="C253" t="inlineStr">
         <is>
           <t>terms-conditions</t>
         </is>
       </c>
-      <c r="D252" t="inlineStr">
+      <c r="D253" t="inlineStr">
         <is>
           <t>core</t>
         </is>
       </c>
-      <c r="E252" t="inlineStr">
+      <c r="E253" t="inlineStr">
         <is>
           <t>User: automation user (location-edit permission)
 Location: test office 1604
 Application: Navigator</t>
         </is>
       </c>
-      <c r="F252" t="inlineStr">
+      <c r="F253" t="inlineStr">
         <is>
           <t>Functional</t>
         </is>
       </c>
-      <c r="G252" t="inlineStr">
+      <c r="G253" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="H252" t="inlineStr">
+      <c r="H253" t="inlineStr">
         <is>
           <t>Automated</t>
         </is>
       </c>
-      <c r="I252" t="inlineStr">
+      <c r="I253" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="J252" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. A save was just completed successfully (form is Clean)</t>
-        </is>
-      </c>
-      <c r="K252" t="inlineStr">
-        <is>
-          <t>1. Click browser Back</t>
-        </is>
-      </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t>Navigation proceeds without any `beforeunload` dialog (form is Clean)</t>
-        </is>
-      </c>
-      <c r="M252" t="inlineStr"/>
-    </row>
-    <row r="253">
-      <c r="A253" t="inlineStr"/>
-      <c r="B253" t="inlineStr"/>
-      <c r="C253" t="inlineStr"/>
-      <c r="D253" t="inlineStr"/>
-      <c r="E253" t="inlineStr"/>
-      <c r="F253" t="inlineStr"/>
-      <c r="G253" t="inlineStr"/>
-      <c r="H253" t="inlineStr"/>
-      <c r="I253" t="inlineStr"/>
-      <c r="J253" t="inlineStr"/>
+      <c r="J253" t="inlineStr">
+        <is>
+          <t>The Terms and Conditions page is open for office 1604. Language filter: All.
+"": empty-vol</t>
+        </is>
+      </c>
       <c r="K253" t="inlineStr">
         <is>
-          <t>2. Click browser Forward to return</t>
+          <t>1. Count all visible rows in the grid</t>
         </is>
       </c>
       <c r="L253" t="inlineStr">
         <is>
-          <t>The T&amp;C page reloads with the saved data intact</t>
+          <t>All rows (~51 including residue) render in a single scroll view — no pagination controls present</t>
         </is>
       </c>
       <c r="M253" t="inlineStr"/>
     </row>
     <row r="254">
-      <c r="A254" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-088</t>
-        </is>
-      </c>
-      <c r="B254" t="inlineStr">
-        <is>
-          <t>Accessibility — logical tab order through page controls</t>
-        </is>
-      </c>
-      <c r="C254" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D254" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E254" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F254" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G254" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H254" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I254" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J254" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default)</t>
-        </is>
-      </c>
+      <c r="A254" t="inlineStr"/>
+      <c r="B254" t="inlineStr"/>
+      <c r="C254" t="inlineStr"/>
+      <c r="D254" t="inlineStr"/>
+      <c r="E254" t="inlineStr"/>
+      <c r="F254" t="inlineStr"/>
+      <c r="G254" t="inlineStr"/>
+      <c r="H254" t="inlineStr"/>
+      <c r="I254" t="inlineStr"/>
+      <c r="J254" t="inlineStr"/>
       <c r="K254" t="inlineStr">
         <is>
-          <t>1. Press Tab repeatedly from the first focusable element</t>
+          <t>2. Scroll to the last row</t>
         </is>
       </c>
       <c r="L254" t="inlineStr">
         <is>
-          <t>Focus moves in a logical order through: Language filter, grid rows (Language dropdown, Name input, column cells), Add row button, Save button</t>
+          <t>The last row is reachable by scrolling; content is read by anchoring on the row's unique name (not index)</t>
         </is>
       </c>
       <c r="M254" t="inlineStr"/>
@@ -10110,495 +10071,47 @@
       <c r="J255" t="inlineStr"/>
       <c r="K255" t="inlineStr">
         <is>
-          <t>2. Verify no focus skips or traps</t>
+          <t>3. Verify no duplicate rows appear</t>
         </is>
       </c>
       <c r="L255" t="inlineStr">
         <is>
-          <t>Every interactive control is reachable via Tab; no element traps focus indefinitely</t>
+          <t>Each row name+language combination is unique across the visible set</t>
         </is>
       </c>
       <c r="M255" t="inlineStr"/>
     </row>
-    <row r="256">
-      <c r="A256" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-089</t>
-        </is>
-      </c>
-      <c r="B256" t="inlineStr">
-        <is>
-          <t>Accessibility — RTE keyboard operability</t>
-        </is>
-      </c>
-      <c r="C256" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D256" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E256" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F256" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G256" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H256" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I256" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="J256" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. A Left Column cell is visible</t>
-        </is>
-      </c>
-      <c r="K256" t="inlineStr">
-        <is>
-          <t>1. Tab into the Left Column cell (or activate it via Enter/Space on the launcher button)</t>
-        </is>
-      </c>
-      <c r="L256" t="inlineStr">
-        <is>
-          <t>The RTE gains focus — the cursor is inside the contenteditable</t>
-        </is>
-      </c>
-      <c r="M256" t="inlineStr"/>
-    </row>
+    <row r="256"/>
     <row r="257">
-      <c r="A257" t="inlineStr"/>
-      <c r="B257" t="inlineStr"/>
-      <c r="C257" t="inlineStr"/>
-      <c r="D257" t="inlineStr"/>
-      <c r="E257" t="inlineStr"/>
-      <c r="F257" t="inlineStr"/>
-      <c r="G257" t="inlineStr"/>
-      <c r="H257" t="inlineStr"/>
-      <c r="I257" t="inlineStr"/>
-      <c r="J257" t="inlineStr"/>
-      <c r="K257" t="inlineStr">
-        <is>
-          <t>2. Type text using the keyboard</t>
-        </is>
-      </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t>Characters appear in the editor</t>
-        </is>
-      </c>
-      <c r="M257" t="inlineStr"/>
-    </row>
-    <row r="258">
-      <c r="A258" t="inlineStr"/>
-      <c r="B258" t="inlineStr"/>
-      <c r="C258" t="inlineStr"/>
-      <c r="D258" t="inlineStr"/>
-      <c r="E258" t="inlineStr"/>
-      <c r="F258" t="inlineStr"/>
-      <c r="G258" t="inlineStr"/>
-      <c r="H258" t="inlineStr"/>
-      <c r="I258" t="inlineStr"/>
-      <c r="J258" t="inlineStr"/>
-      <c r="K258" t="inlineStr">
-        <is>
-          <t>3. Press Tab or Escape to exit the editor</t>
-        </is>
-      </c>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t>Focus moves OUT of the contenteditable to the next focusable element — the editor does not trap keyboard focus</t>
-        </is>
-      </c>
-      <c r="M258" t="inlineStr"/>
-    </row>
-    <row r="259">
-      <c r="A259" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-090</t>
-        </is>
-      </c>
-      <c r="B259" t="inlineStr">
-        <is>
-          <t>Accessibility — unsaved-changes dialog focus trap and restore</t>
-        </is>
-      </c>
-      <c r="C259" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D259" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E259" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F259" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G259" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H259" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I259" t="inlineStr">
-        <is>
-          <t>Skipped</t>
-        </is>
-      </c>
-      <c r="J259" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. The form is dirty. The language filter is about to be changed (triggers the guard dialog)</t>
-        </is>
-      </c>
-      <c r="K259" t="inlineStr">
-        <is>
-          <t>1. Select a language filter option to trigger the guard dialog</t>
-        </is>
-      </c>
-      <c r="L259" t="inlineStr">
-        <is>
-          <t>The warning dialog appears; keyboard focus moves into it (accessibility focus behavior)</t>
-        </is>
-      </c>
-      <c r="M259" t="inlineStr"/>
-    </row>
-    <row r="260">
-      <c r="A260" t="inlineStr"/>
-      <c r="B260" t="inlineStr"/>
-      <c r="C260" t="inlineStr"/>
-      <c r="D260" t="inlineStr"/>
-      <c r="E260" t="inlineStr"/>
-      <c r="F260" t="inlineStr"/>
-      <c r="G260" t="inlineStr"/>
-      <c r="H260" t="inlineStr"/>
-      <c r="I260" t="inlineStr"/>
-      <c r="J260" t="inlineStr"/>
-      <c r="K260" t="inlineStr">
-        <is>
-          <t>2. Press Tab within the dialog</t>
-        </is>
-      </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t>Focus cycles between Stay and Discard buttons (focus trapped within dialog)</t>
-        </is>
-      </c>
-      <c r="M260" t="inlineStr"/>
-    </row>
-    <row r="261">
-      <c r="A261" t="inlineStr"/>
-      <c r="B261" t="inlineStr"/>
-      <c r="C261" t="inlineStr"/>
-      <c r="D261" t="inlineStr"/>
-      <c r="E261" t="inlineStr"/>
-      <c r="F261" t="inlineStr"/>
-      <c r="G261" t="inlineStr"/>
-      <c r="H261" t="inlineStr"/>
-      <c r="I261" t="inlineStr"/>
-      <c r="J261" t="inlineStr"/>
-      <c r="K261" t="inlineStr">
-        <is>
-          <t>3. Press Escape or click Stay</t>
-        </is>
-      </c>
-      <c r="L261" t="inlineStr">
-        <is>
-          <t>The dialog closes; focus returns to the element that triggered the dialog (the language filter)</t>
-        </is>
-      </c>
-      <c r="M261" t="inlineStr"/>
-    </row>
-    <row r="262">
-      <c r="A262" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-091</t>
-        </is>
-      </c>
-      <c r="B262" t="inlineStr">
-        <is>
-          <t>Network payload — PUT response body reflects committed data</t>
-        </is>
-      </c>
-      <c r="C262" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D262" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E262" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator
-Sample input 1: "NET-PAYLOAD-TEST"
-Sample input 2: "PAYLOAD-CONTENT"</t>
-        </is>
-      </c>
-      <c r="F262" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G262" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H262" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I262" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J262" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language: US English (default). A row has been edited with a known Name and known RTE content. Network interception captures request and response.
-"": persistence</t>
-        </is>
-      </c>
-      <c r="K262" t="inlineStr">
-        <is>
-          <t>1. Edit a row: set Name to "NET-PAYLOAD-TEST", type "PAYLOAD-CONTENT" into Left Column</t>
-        </is>
-      </c>
-      <c r="L262" t="inlineStr">
-        <is>
-          <t>Save becomes enabled</t>
-        </is>
-      </c>
-      <c r="M262" t="inlineStr"/>
-    </row>
-    <row r="263">
-      <c r="A263" t="inlineStr"/>
-      <c r="B263" t="inlineStr"/>
-      <c r="C263" t="inlineStr"/>
-      <c r="D263" t="inlineStr"/>
-      <c r="E263" t="inlineStr"/>
-      <c r="F263" t="inlineStr"/>
-      <c r="G263" t="inlineStr"/>
-      <c r="H263" t="inlineStr"/>
-      <c r="I263" t="inlineStr"/>
-      <c r="J263" t="inlineStr"/>
-      <c r="K263" t="inlineStr">
-        <is>
-          <t>2. Click Save and capture the save request payload</t>
-        </is>
-      </c>
-      <c r="L263" t="inlineStr">
-        <is>
-          <t>The request body contains: the edited row with `"languageId":"en-US"`, the name "NET-PAYLOAD-TEST", and the RTE content (HTML-escaped)</t>
-        </is>
-      </c>
-      <c r="M263" t="inlineStr"/>
-    </row>
-    <row r="264">
-      <c r="A264" t="inlineStr"/>
-      <c r="B264" t="inlineStr"/>
-      <c r="C264" t="inlineStr"/>
-      <c r="D264" t="inlineStr"/>
-      <c r="E264" t="inlineStr"/>
-      <c r="F264" t="inlineStr"/>
-      <c r="G264" t="inlineStr"/>
-      <c r="H264" t="inlineStr"/>
-      <c r="I264" t="inlineStr"/>
-      <c r="J264" t="inlineStr"/>
-      <c r="K264" t="inlineStr">
-        <is>
-          <t>3. Capture the response body</t>
-        </is>
-      </c>
-      <c r="L264" t="inlineStr">
-        <is>
-          <t>The response reflects the committed payload — the saved row data appears in the response with matching `languageId`, name, and content</t>
-        </is>
-      </c>
-      <c r="M264" t="inlineStr"/>
-    </row>
-    <row r="265">
-      <c r="A265" t="inlineStr">
-        <is>
-          <t>TC-TNC-CORE-092</t>
-        </is>
-      </c>
-      <c r="B265" t="inlineStr">
-        <is>
-          <t>Volume — all rows render in one scroll view without pagination</t>
-        </is>
-      </c>
-      <c r="C265" t="inlineStr">
-        <is>
-          <t>terms-conditions</t>
-        </is>
-      </c>
-      <c r="D265" t="inlineStr">
-        <is>
-          <t>core</t>
-        </is>
-      </c>
-      <c r="E265" t="inlineStr">
-        <is>
-          <t>User: automation user (location-edit permission)
-Location: test office 1604
-Application: Navigator</t>
-        </is>
-      </c>
-      <c r="F265" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="G265" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="H265" t="inlineStr">
-        <is>
-          <t>Automated</t>
-        </is>
-      </c>
-      <c r="I265" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="J265" t="inlineStr">
-        <is>
-          <t>The Terms and Conditions page is open for office 1604. Language filter: All.
-"": empty-vol</t>
-        </is>
-      </c>
-      <c r="K265" t="inlineStr">
-        <is>
-          <t>1. Count all visible rows in the grid</t>
-        </is>
-      </c>
-      <c r="L265" t="inlineStr">
-        <is>
-          <t>All rows (~51 including residue) render in a single scroll view — no pagination controls present</t>
-        </is>
-      </c>
-      <c r="M265" t="inlineStr"/>
-    </row>
-    <row r="266">
-      <c r="A266" t="inlineStr"/>
-      <c r="B266" t="inlineStr"/>
-      <c r="C266" t="inlineStr"/>
-      <c r="D266" t="inlineStr"/>
-      <c r="E266" t="inlineStr"/>
-      <c r="F266" t="inlineStr"/>
-      <c r="G266" t="inlineStr"/>
-      <c r="H266" t="inlineStr"/>
-      <c r="I266" t="inlineStr"/>
-      <c r="J266" t="inlineStr"/>
-      <c r="K266" t="inlineStr">
-        <is>
-          <t>2. Scroll to the last row</t>
-        </is>
-      </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t>The last row is reachable by scrolling; content is read by anchoring on the row's unique name (not index)</t>
-        </is>
-      </c>
-      <c r="M266" t="inlineStr"/>
-    </row>
-    <row r="267">
-      <c r="A267" t="inlineStr"/>
-      <c r="B267" t="inlineStr"/>
-      <c r="C267" t="inlineStr"/>
-      <c r="D267" t="inlineStr"/>
-      <c r="E267" t="inlineStr"/>
-      <c r="F267" t="inlineStr"/>
-      <c r="G267" t="inlineStr"/>
-      <c r="H267" t="inlineStr"/>
-      <c r="I267" t="inlineStr"/>
-      <c r="J267" t="inlineStr"/>
-      <c r="K267" t="inlineStr">
-        <is>
-          <t>3. Verify no duplicate rows appear</t>
-        </is>
-      </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t>Each row name+language combination is unique across the visible set</t>
-        </is>
-      </c>
-      <c r="M267" t="inlineStr"/>
-    </row>
-    <row r="268"/>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
+      <c r="A257" s="2" t="inlineStr">
         <is>
           <t>SUMMARY</t>
         </is>
       </c>
-      <c r="B269" s="2" t="inlineStr">
+      <c r="B257" s="2" t="inlineStr">
         <is>
           <t>Terms and Conditions — Core</t>
         </is>
       </c>
-      <c r="C269" s="2" t="inlineStr"/>
-      <c r="D269" s="2" t="inlineStr"/>
-      <c r="E269" s="2" t="inlineStr"/>
-      <c r="F269" s="2" t="inlineStr"/>
-      <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="2" t="inlineStr">
-        <is>
-          <t>Automated: 87 / Pending: 5</t>
-        </is>
-      </c>
-      <c r="I269" s="2" t="inlineStr">
+      <c r="C257" s="2" t="inlineStr"/>
+      <c r="D257" s="2" t="inlineStr"/>
+      <c r="E257" s="2" t="inlineStr"/>
+      <c r="F257" s="2" t="inlineStr"/>
+      <c r="G257" s="2" t="inlineStr"/>
+      <c r="H257" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Automated: 87 / Pending: 0</t>
+        </is>
+      </c>
+      <c r="I257" s="2" t="inlineStr">
         <is>
           <t>Pass:77 Fail:0 Skipped:10 Blocked:0</t>
         </is>
       </c>
-      <c r="J269" s="2" t="inlineStr"/>
-      <c r="K269" s="2" t="inlineStr"/>
-      <c r="L269" s="2" t="inlineStr"/>
-      <c r="M269" s="2" t="inlineStr">
+      <c r="J257" s="2" t="inlineStr"/>
+      <c r="K257" s="2" t="inlineStr"/>
+      <c r="L257" s="2" t="inlineStr"/>
+      <c r="M257" s="2" t="inlineStr">
         <is>
           <t>Last Updated: 2026-08-18</t>
         </is>
